--- a/research/traditional_assets/database/data/malaysia/malaysia_software_internet.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_software_internet.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1208178215918815</v>
+        <v>0.120562058820061</v>
       </c>
       <c r="C2">
-        <v>77.73527187973657</v>
+        <v>77.21575193959657</v>
       </c>
       <c r="D2">
-        <v>75.44527187973657</v>
+        <v>75.70337193959656</v>
       </c>
       <c r="E2">
-        <v>-0.162</v>
+        <v>0.6156199999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.77762</v>
       </c>
       <c r="G2">
         <v>2.29</v>
@@ -1570,28 +1570,28 @@
         <v>7.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.039114286</v>
       </c>
       <c r="N2">
-        <v>7.4</v>
+        <v>7.360885714</v>
       </c>
       <c r="O2">
-        <v>1.776</v>
+        <v>1.76661257136</v>
       </c>
       <c r="P2">
-        <v>5.624000000000001</v>
+        <v>5.594273142640001</v>
       </c>
       <c r="Q2">
-        <v>6.554</v>
+        <v>6.52427314264</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1208178215918815</v>
+        <v>0.1213937159798596</v>
       </c>
       <c r="T2">
-        <v>1.264908244262672</v>
+        <v>1.274618650986305</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>189.1891878072375</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.120562058820061</v>
+        <v>0.1203062960482404</v>
       </c>
       <c r="C3">
-        <v>77.21575193959657</v>
+        <v>76.69800399431385</v>
       </c>
       <c r="D3">
-        <v>75.70337193959656</v>
+        <v>75.96324399431384</v>
       </c>
       <c r="E3">
-        <v>0.6156199999999999</v>
+        <v>1.39324</v>
       </c>
       <c r="F3">
-        <v>0.77762</v>
+        <v>1.55524</v>
       </c>
       <c r="G3">
         <v>2.29</v>
@@ -1652,28 +1652,28 @@
         <v>7.4</v>
       </c>
       <c r="M3">
-        <v>0.039114286</v>
+        <v>0.078228572</v>
       </c>
       <c r="N3">
-        <v>7.360885714</v>
+        <v>7.321771428</v>
       </c>
       <c r="O3">
-        <v>1.76661257136</v>
+        <v>1.75722514272</v>
       </c>
       <c r="P3">
-        <v>5.594273142640001</v>
+        <v>5.564546285280001</v>
       </c>
       <c r="Q3">
-        <v>6.52427314264</v>
+        <v>6.49454628528</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1213937159798596</v>
+        <v>0.1219813633145311</v>
       </c>
       <c r="T3">
-        <v>1.274618650986305</v>
+        <v>1.284527229275726</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>189.1891878072375</v>
+        <v>94.59459390361874</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1203062960482404</v>
+        <v>0.12005053327642</v>
       </c>
       <c r="C4">
-        <v>76.69800399431385</v>
+        <v>76.18204635528483</v>
       </c>
       <c r="D4">
-        <v>75.96324399431384</v>
+        <v>76.22490635528482</v>
       </c>
       <c r="E4">
-        <v>1.39324</v>
+        <v>2.17086</v>
       </c>
       <c r="F4">
-        <v>1.55524</v>
+        <v>2.33286</v>
       </c>
       <c r="G4">
         <v>2.29</v>
@@ -1734,28 +1734,28 @@
         <v>7.4</v>
       </c>
       <c r="M4">
-        <v>0.078228572</v>
+        <v>0.117342858</v>
       </c>
       <c r="N4">
-        <v>7.321771428</v>
+        <v>7.282657142000001</v>
       </c>
       <c r="O4">
-        <v>1.75722514272</v>
+        <v>1.74783771408</v>
       </c>
       <c r="P4">
-        <v>5.564546285280001</v>
+        <v>5.53481942792</v>
       </c>
       <c r="Q4">
-        <v>6.49454628528</v>
+        <v>6.46481942792</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1219813633145311</v>
+        <v>0.1225811270890927</v>
       </c>
       <c r="T4">
-        <v>1.284527229275726</v>
+        <v>1.294640108148434</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>94.59459390361874</v>
+        <v>63.06306260241251</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.12005053327642</v>
+        <v>0.1197947705045994</v>
       </c>
       <c r="C5">
-        <v>76.18204635528483</v>
+        <v>75.6678975870792</v>
       </c>
       <c r="D5">
-        <v>76.22490635528482</v>
+        <v>76.48837758707919</v>
       </c>
       <c r="E5">
-        <v>2.17086</v>
+        <v>2.94848</v>
       </c>
       <c r="F5">
-        <v>2.33286</v>
+        <v>3.11048</v>
       </c>
       <c r="G5">
         <v>2.29</v>
@@ -1816,28 +1816,28 @@
         <v>7.4</v>
       </c>
       <c r="M5">
-        <v>0.117342858</v>
+        <v>0.156457144</v>
       </c>
       <c r="N5">
-        <v>7.282657142000001</v>
+        <v>7.243542856</v>
       </c>
       <c r="O5">
-        <v>1.74783771408</v>
+        <v>1.73845028544</v>
       </c>
       <c r="P5">
-        <v>5.53481942792</v>
+        <v>5.50509257056</v>
       </c>
       <c r="Q5">
-        <v>6.46481942792</v>
+        <v>6.43509257056</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1225811270890927</v>
+        <v>0.1231933859422911</v>
       </c>
       <c r="T5">
-        <v>1.294640108148434</v>
+        <v>1.304963671997657</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.06306260241251</v>
+        <v>47.29729695180938</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1197947705045994</v>
+        <v>0.1195390077327789</v>
       </c>
       <c r="C6">
-        <v>75.6678975870792</v>
+        <v>75.15557651183039</v>
       </c>
       <c r="D6">
-        <v>76.48837758707919</v>
+        <v>76.75367651183038</v>
       </c>
       <c r="E6">
-        <v>2.94848</v>
+        <v>3.7261</v>
       </c>
       <c r="F6">
-        <v>3.11048</v>
+        <v>3.8881</v>
       </c>
       <c r="G6">
         <v>2.29</v>
@@ -1898,28 +1898,28 @@
         <v>7.4</v>
       </c>
       <c r="M6">
-        <v>0.156457144</v>
+        <v>0.19557143</v>
       </c>
       <c r="N6">
-        <v>7.243542856</v>
+        <v>7.20442857</v>
       </c>
       <c r="O6">
-        <v>1.73845028544</v>
+        <v>1.7290628568</v>
       </c>
       <c r="P6">
-        <v>5.50509257056</v>
+        <v>5.4753657132</v>
       </c>
       <c r="Q6">
-        <v>6.43509257056</v>
+        <v>6.4053657132</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1231933859422911</v>
+        <v>0.1238185344555567</v>
       </c>
       <c r="T6">
-        <v>1.304963671997657</v>
+        <v>1.315504574033179</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.29729695180938</v>
+        <v>37.8378375614475</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1195390077327789</v>
+        <v>0.1192832449609584</v>
       </c>
       <c r="C7">
-        <v>75.15557651183039</v>
+        <v>74.64510221371808</v>
       </c>
       <c r="D7">
-        <v>76.75367651183038</v>
+        <v>77.02082221371806</v>
       </c>
       <c r="E7">
-        <v>3.7261</v>
+        <v>4.50372</v>
       </c>
       <c r="F7">
-        <v>3.8881</v>
+        <v>4.66572</v>
       </c>
       <c r="G7">
         <v>2.29</v>
@@ -1980,28 +1980,28 @@
         <v>7.4</v>
       </c>
       <c r="M7">
-        <v>0.19557143</v>
+        <v>0.234685716</v>
       </c>
       <c r="N7">
-        <v>7.20442857</v>
+        <v>7.165314284</v>
       </c>
       <c r="O7">
-        <v>1.7290628568</v>
+        <v>1.71967542816</v>
       </c>
       <c r="P7">
-        <v>5.4753657132</v>
+        <v>5.44563885584</v>
       </c>
       <c r="Q7">
-        <v>6.4053657132</v>
+        <v>6.37563885584</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1238185344555567</v>
+        <v>0.1244569840010196</v>
       </c>
       <c r="T7">
-        <v>1.315504574033179</v>
+        <v>1.326269750580096</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.8378375614475</v>
+        <v>31.53153130120625</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1192832449609584</v>
+        <v>0.1190274821891379</v>
       </c>
       <c r="C8">
-        <v>74.64510221371808</v>
+        <v>74.13649404354442</v>
       </c>
       <c r="D8">
-        <v>77.02082221371806</v>
+        <v>77.2898340435444</v>
       </c>
       <c r="E8">
-        <v>4.50372</v>
+        <v>5.281339999999999</v>
       </c>
       <c r="F8">
-        <v>4.665719999999999</v>
+        <v>5.443339999999999</v>
       </c>
       <c r="G8">
         <v>2.29</v>
@@ -2062,28 +2062,28 @@
         <v>7.4</v>
       </c>
       <c r="M8">
-        <v>0.234685716</v>
+        <v>0.2738000019999999</v>
       </c>
       <c r="N8">
-        <v>7.165314284000001</v>
+        <v>7.126199998000001</v>
       </c>
       <c r="O8">
-        <v>1.71967542816</v>
+        <v>1.71028799952</v>
       </c>
       <c r="P8">
-        <v>5.44563885584</v>
+        <v>5.41591199848</v>
       </c>
       <c r="Q8">
-        <v>6.37563885584</v>
+        <v>6.34591199848</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1244569840010196</v>
+        <v>0.1251091636442343</v>
       </c>
       <c r="T8">
-        <v>1.326269750580096</v>
+        <v>1.337266436300064</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.53153130120626</v>
+        <v>27.02702682960537</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1190274821891379</v>
+        <v>0.1187717194173173</v>
       </c>
       <c r="C9">
-        <v>74.13649404354442</v>
+        <v>73.6297716234065</v>
       </c>
       <c r="D9">
-        <v>77.28983404354442</v>
+        <v>77.5607316234065</v>
       </c>
       <c r="E9">
-        <v>5.281340000000001</v>
+        <v>6.05896</v>
       </c>
       <c r="F9">
-        <v>5.443340000000001</v>
+        <v>6.22096</v>
       </c>
       <c r="G9">
         <v>2.29</v>
@@ -2144,28 +2144,28 @@
         <v>7.4</v>
       </c>
       <c r="M9">
-        <v>0.273800002</v>
+        <v>0.312914288</v>
       </c>
       <c r="N9">
-        <v>7.126199998000001</v>
+        <v>7.087085712</v>
       </c>
       <c r="O9">
-        <v>1.71028799952</v>
+        <v>1.70090057088</v>
       </c>
       <c r="P9">
-        <v>5.41591199848</v>
+        <v>5.38618514112</v>
       </c>
       <c r="Q9">
-        <v>6.34591199848</v>
+        <v>6.31618514112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1251091636442343</v>
+        <v>0.1257755211057797</v>
       </c>
       <c r="T9">
-        <v>1.337266436300064</v>
+        <v>1.348502180405249</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.02702682960535</v>
+        <v>23.64864847590469</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1187717194173173</v>
+        <v>0.1185159566454968</v>
       </c>
       <c r="C10">
-        <v>73.6297716234065</v>
+        <v>73.12495485146739</v>
       </c>
       <c r="D10">
-        <v>77.5607316234065</v>
+        <v>77.83353485146739</v>
       </c>
       <c r="E10">
-        <v>6.05896</v>
+        <v>6.83658</v>
       </c>
       <c r="F10">
-        <v>6.22096</v>
+        <v>6.99858</v>
       </c>
       <c r="G10">
         <v>2.29</v>
@@ -2226,28 +2226,28 @@
         <v>7.4</v>
       </c>
       <c r="M10">
-        <v>0.312914288</v>
+        <v>0.352028574</v>
       </c>
       <c r="N10">
-        <v>7.087085712</v>
+        <v>7.047971426</v>
       </c>
       <c r="O10">
-        <v>1.70090057088</v>
+        <v>1.69151314224</v>
       </c>
       <c r="P10">
-        <v>5.38618514112</v>
+        <v>5.35645828376</v>
       </c>
       <c r="Q10">
-        <v>6.31618514112</v>
+        <v>6.28645828376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1257755211057797</v>
+        <v>0.1264565237862603</v>
       </c>
       <c r="T10">
-        <v>1.348502180405249</v>
+        <v>1.359984863941317</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.64864847590469</v>
+        <v>21.02102086747083</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1185159566454968</v>
+        <v>0.1182601938736764</v>
       </c>
       <c r="C11">
-        <v>73.12495485146739</v>
+        <v>72.6220639068285</v>
       </c>
       <c r="D11">
-        <v>77.83353485146739</v>
+        <v>78.1082639068285</v>
       </c>
       <c r="E11">
-        <v>6.83658</v>
+        <v>7.614199999999999</v>
       </c>
       <c r="F11">
-        <v>6.99858</v>
+        <v>7.776199999999999</v>
       </c>
       <c r="G11">
         <v>2.29</v>
@@ -2308,28 +2308,28 @@
         <v>7.4</v>
       </c>
       <c r="M11">
-        <v>0.352028574</v>
+        <v>0.3911428599999999</v>
       </c>
       <c r="N11">
-        <v>7.047971426</v>
+        <v>7.008857140000001</v>
       </c>
       <c r="O11">
-        <v>1.69151314224</v>
+        <v>1.6821257136</v>
       </c>
       <c r="P11">
-        <v>5.35645828376</v>
+        <v>5.3267314264</v>
       </c>
       <c r="Q11">
-        <v>6.28645828376</v>
+        <v>6.2567314264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1264565237862603</v>
+        <v>0.1271526598596404</v>
       </c>
       <c r="T11">
-        <v>1.359984863941317</v>
+        <v>1.371722718222632</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.02102086747083</v>
+        <v>18.91891878072375</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1182601938736764</v>
+        <v>0.1180044311018558</v>
       </c>
       <c r="C12">
-        <v>72.6220639068285</v>
+        <v>72.12111925450515</v>
       </c>
       <c r="D12">
-        <v>78.1082639068285</v>
+        <v>78.38493925450514</v>
       </c>
       <c r="E12">
-        <v>7.6142</v>
+        <v>8.391819999999999</v>
       </c>
       <c r="F12">
-        <v>7.7762</v>
+        <v>8.55382</v>
       </c>
       <c r="G12">
         <v>2.29</v>
@@ -2390,28 +2390,28 @@
         <v>7.4</v>
       </c>
       <c r="M12">
-        <v>0.39114286</v>
+        <v>0.430257146</v>
       </c>
       <c r="N12">
-        <v>7.00885714</v>
+        <v>6.969742854000001</v>
       </c>
       <c r="O12">
-        <v>1.6821257136</v>
+        <v>1.67273828496</v>
       </c>
       <c r="P12">
-        <v>5.3267314264</v>
+        <v>5.29700456904</v>
       </c>
       <c r="Q12">
-        <v>6.2567314264</v>
+        <v>6.22700456904</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1271526598596404</v>
+        <v>0.1278644394402874</v>
       </c>
       <c r="T12">
-        <v>1.371722718222632</v>
+        <v>1.383724344510267</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.91891878072375</v>
+        <v>17.19901707338523</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1180044311018558</v>
+        <v>0.1177486683300353</v>
       </c>
       <c r="C13">
-        <v>72.12111925450515</v>
+        <v>71.62214165050828</v>
       </c>
       <c r="D13">
-        <v>78.38493925450514</v>
+        <v>78.66358165050828</v>
       </c>
       <c r="E13">
-        <v>8.391819999999999</v>
+        <v>9.169439999999998</v>
       </c>
       <c r="F13">
-        <v>8.55382</v>
+        <v>9.331439999999999</v>
       </c>
       <c r="G13">
         <v>2.29</v>
@@ -2472,28 +2472,28 @@
         <v>7.4</v>
       </c>
       <c r="M13">
-        <v>0.430257146</v>
+        <v>0.4693714319999999</v>
       </c>
       <c r="N13">
-        <v>6.969742854000001</v>
+        <v>6.930628568</v>
       </c>
       <c r="O13">
-        <v>1.67273828496</v>
+        <v>1.66335085632</v>
       </c>
       <c r="P13">
-        <v>5.29700456904</v>
+        <v>5.26727771168</v>
       </c>
       <c r="Q13">
-        <v>6.22700456904</v>
+        <v>6.19727771168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1278644394402874</v>
+        <v>0.1285923958295856</v>
       </c>
       <c r="T13">
-        <v>1.383724344510267</v>
+        <v>1.395998735031713</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.19901707338523</v>
+        <v>15.76576565060313</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1177486683300353</v>
+        <v>0.1174929055582148</v>
       </c>
       <c r="C14">
-        <v>71.62214165050828</v>
+        <v>71.12515214703525</v>
       </c>
       <c r="D14">
-        <v>78.66358165050828</v>
+        <v>78.94421214703524</v>
       </c>
       <c r="E14">
-        <v>9.169439999999998</v>
+        <v>9.94706</v>
       </c>
       <c r="F14">
-        <v>9.331439999999999</v>
+        <v>10.10906</v>
       </c>
       <c r="G14">
         <v>2.29</v>
@@ -2554,28 +2554,28 @@
         <v>7.4</v>
       </c>
       <c r="M14">
-        <v>0.4693714319999999</v>
+        <v>0.5084857180000001</v>
       </c>
       <c r="N14">
-        <v>6.930628568</v>
+        <v>6.891514282</v>
       </c>
       <c r="O14">
-        <v>1.66335085632</v>
+        <v>1.65396342768</v>
       </c>
       <c r="P14">
-        <v>5.26727771168</v>
+        <v>5.23755085432</v>
       </c>
       <c r="Q14">
-        <v>6.19727771168</v>
+        <v>6.16755085432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1285923958295856</v>
+        <v>0.1293370868485227</v>
       </c>
       <c r="T14">
-        <v>1.395998735031713</v>
+        <v>1.408555295450204</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.76576565060313</v>
+        <v>14.55301444671057</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1174929055582148</v>
+        <v>0.1172371427863943</v>
       </c>
       <c r="C15">
-        <v>71.12515214703525</v>
+        <v>70.63017209777189</v>
       </c>
       <c r="D15">
-        <v>78.94421214703524</v>
+        <v>79.22685209777188</v>
       </c>
       <c r="E15">
-        <v>9.94706</v>
+        <v>10.72468</v>
       </c>
       <c r="F15">
-        <v>10.10906</v>
+        <v>10.88668</v>
       </c>
       <c r="G15">
         <v>2.29</v>
@@ -2636,28 +2636,28 @@
         <v>7.4</v>
       </c>
       <c r="M15">
-        <v>0.5084857180000001</v>
+        <v>0.5476000040000001</v>
       </c>
       <c r="N15">
-        <v>6.891514282</v>
+        <v>6.852399996</v>
       </c>
       <c r="O15">
-        <v>1.65396342768</v>
+        <v>1.64457599904</v>
       </c>
       <c r="P15">
-        <v>5.23755085432</v>
+        <v>5.20782399696</v>
       </c>
       <c r="Q15">
-        <v>6.16755085432</v>
+        <v>6.13782399696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1293370868485227</v>
+        <v>0.1300990962632491</v>
       </c>
       <c r="T15">
-        <v>1.408555295450204</v>
+        <v>1.421403868901682</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.55301444671057</v>
+        <v>13.51351341480268</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1172371427863943</v>
+        <v>0.1171523800145737</v>
       </c>
       <c r="C16">
-        <v>70.63017209777189</v>
+        <v>69.94666931691791</v>
       </c>
       <c r="D16">
-        <v>79.22685209777188</v>
+        <v>79.3209693169179</v>
       </c>
       <c r="E16">
-        <v>10.72468</v>
+        <v>11.5023</v>
       </c>
       <c r="F16">
-        <v>10.88668</v>
+        <v>11.6643</v>
       </c>
       <c r="G16">
         <v>2.29</v>
@@ -2718,45 +2718,45 @@
         <v>7.4</v>
       </c>
       <c r="M16">
-        <v>0.5476000040000001</v>
+        <v>0.6042107400000001</v>
       </c>
       <c r="N16">
-        <v>6.852399996</v>
+        <v>6.79578926</v>
       </c>
       <c r="O16">
-        <v>1.64457599904</v>
+        <v>1.6309894224</v>
       </c>
       <c r="P16">
-        <v>5.20782399696</v>
+        <v>5.1647998376</v>
       </c>
       <c r="Q16">
-        <v>6.13782399696</v>
+        <v>6.0947998376</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1300990962632491</v>
+        <v>0.1308790353112632</v>
       </c>
       <c r="T16">
-        <v>1.421403868901682</v>
+        <v>1.43455476172849</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.51351341480268</v>
+        <v>12.24738242819053</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1171523800145737</v>
+        <v>0.1169080172427532</v>
       </c>
       <c r="C17">
-        <v>69.94666931691793</v>
+        <v>69.44163590669162</v>
       </c>
       <c r="D17">
-        <v>79.32096931691792</v>
+        <v>79.59355590669161</v>
       </c>
       <c r="E17">
-        <v>11.5023</v>
+        <v>12.27992</v>
       </c>
       <c r="F17">
-        <v>11.6643</v>
+        <v>12.44192</v>
       </c>
       <c r="G17">
         <v>2.29</v>
@@ -2800,28 +2800,28 @@
         <v>7.4</v>
       </c>
       <c r="M17">
-        <v>0.60421074</v>
+        <v>0.644491456</v>
       </c>
       <c r="N17">
-        <v>6.79578926</v>
+        <v>6.755508544</v>
       </c>
       <c r="O17">
-        <v>1.6309894224</v>
+        <v>1.62132205056</v>
       </c>
       <c r="P17">
-        <v>5.1647998376</v>
+        <v>5.134186493440001</v>
       </c>
       <c r="Q17">
-        <v>6.0947998376</v>
+        <v>6.06418649344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1308790353112632</v>
+        <v>0.131677544336611</v>
       </c>
       <c r="T17">
-        <v>1.43455476172849</v>
+        <v>1.448018771051174</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.24738242819054</v>
+        <v>11.48192102642863</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1169080172427532</v>
+        <v>0.1166636544709327</v>
       </c>
       <c r="C18">
-        <v>69.44163590669162</v>
+        <v>68.93848244508312</v>
       </c>
       <c r="D18">
-        <v>79.59355590669161</v>
+        <v>79.86802244508311</v>
       </c>
       <c r="E18">
-        <v>12.27992</v>
+        <v>13.05754</v>
       </c>
       <c r="F18">
-        <v>12.44192</v>
+        <v>13.21954</v>
       </c>
       <c r="G18">
         <v>2.29</v>
@@ -2882,28 +2882,28 @@
         <v>7.4</v>
       </c>
       <c r="M18">
-        <v>0.644491456</v>
+        <v>0.684772172</v>
       </c>
       <c r="N18">
-        <v>6.755508544</v>
+        <v>6.715227828000001</v>
       </c>
       <c r="O18">
-        <v>1.62132205056</v>
+        <v>1.61165467872</v>
       </c>
       <c r="P18">
-        <v>5.134186493440001</v>
+        <v>5.103573149280001</v>
       </c>
       <c r="Q18">
-        <v>6.06418649344</v>
+        <v>6.03357314928</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.131677544336611</v>
+        <v>0.1324952945432925</v>
       </c>
       <c r="T18">
-        <v>1.448018771051174</v>
+        <v>1.46180721433344</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.48192102642863</v>
+        <v>10.80651390722694</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1166636544709327</v>
+        <v>0.1164192916991122</v>
       </c>
       <c r="C19">
-        <v>68.93848244508312</v>
+        <v>68.43722844755817</v>
       </c>
       <c r="D19">
-        <v>79.86802244508311</v>
+        <v>80.14438844755817</v>
       </c>
       <c r="E19">
-        <v>13.05754</v>
+        <v>13.83516</v>
       </c>
       <c r="F19">
-        <v>13.21954</v>
+        <v>13.99716</v>
       </c>
       <c r="G19">
         <v>2.29</v>
@@ -2964,28 +2964,28 @@
         <v>7.4</v>
       </c>
       <c r="M19">
-        <v>0.684772172</v>
+        <v>0.725052888</v>
       </c>
       <c r="N19">
-        <v>6.715227828000001</v>
+        <v>6.674947112</v>
       </c>
       <c r="O19">
-        <v>1.61165467872</v>
+        <v>1.60198730688</v>
       </c>
       <c r="P19">
-        <v>5.103573149280001</v>
+        <v>5.07295980512</v>
       </c>
       <c r="Q19">
-        <v>6.03357314928</v>
+        <v>6.00295980512</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1324952945432925</v>
+        <v>0.1333329898769661</v>
       </c>
       <c r="T19">
-        <v>1.46180721433344</v>
+        <v>1.475931961110396</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.80651390722694</v>
+        <v>10.20615202349211</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1164192916991122</v>
+        <v>0.1164204089272917</v>
       </c>
       <c r="C20">
-        <v>68.4372284475582</v>
+        <v>67.65834054822767</v>
       </c>
       <c r="D20">
-        <v>80.14438844755819</v>
+        <v>80.14312054822766</v>
       </c>
       <c r="E20">
-        <v>13.83516</v>
+        <v>14.61278</v>
       </c>
       <c r="F20">
-        <v>13.99716</v>
+        <v>14.77478</v>
       </c>
       <c r="G20">
         <v>2.29</v>
@@ -3046,45 +3046,45 @@
         <v>7.4</v>
       </c>
       <c r="M20">
-        <v>0.7250528879999999</v>
+        <v>0.79045073</v>
       </c>
       <c r="N20">
-        <v>6.674947112000001</v>
+        <v>6.60954927</v>
       </c>
       <c r="O20">
-        <v>1.60198730688</v>
+        <v>1.5862918248</v>
       </c>
       <c r="P20">
-        <v>5.072959805120001</v>
+        <v>5.023257445200001</v>
       </c>
       <c r="Q20">
-        <v>6.002959805120001</v>
+        <v>5.9532574452</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1333329898769661</v>
+        <v>0.1341913690460391</v>
       </c>
       <c r="T20">
-        <v>1.475931961110396</v>
+        <v>1.49040546706703</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.20615202349211</v>
+        <v>9.361747315990208</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1164204089272917</v>
+        <v>0.1161889661554712</v>
       </c>
       <c r="C21">
-        <v>67.65834054822767</v>
+        <v>67.1442355133581</v>
       </c>
       <c r="D21">
-        <v>80.14312054822766</v>
+        <v>80.4066355133581</v>
       </c>
       <c r="E21">
-        <v>14.61278</v>
+        <v>15.3904</v>
       </c>
       <c r="F21">
-        <v>14.77478</v>
+        <v>15.5524</v>
       </c>
       <c r="G21">
         <v>2.29</v>
@@ -3128,28 +3128,28 @@
         <v>7.4</v>
       </c>
       <c r="M21">
-        <v>0.79045073</v>
+        <v>0.8320534000000001</v>
       </c>
       <c r="N21">
-        <v>6.60954927</v>
+        <v>6.5679466</v>
       </c>
       <c r="O21">
-        <v>1.5862918248</v>
+        <v>1.576307184</v>
       </c>
       <c r="P21">
-        <v>5.023257445200001</v>
+        <v>4.991639416</v>
       </c>
       <c r="Q21">
-        <v>5.9532574452</v>
+        <v>5.921639416</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1341913690460391</v>
+        <v>0.135071207694339</v>
       </c>
       <c r="T21">
-        <v>1.49040546706703</v>
+        <v>1.50524081067258</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.361747315990208</v>
+        <v>8.893659950190695</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1161889661554712</v>
+        <v>0.1159575233836507</v>
       </c>
       <c r="C22">
-        <v>67.1442355133581</v>
+        <v>66.63186909841139</v>
       </c>
       <c r="D22">
-        <v>80.4066355133581</v>
+        <v>80.67188909841138</v>
       </c>
       <c r="E22">
-        <v>15.3904</v>
+        <v>16.16802</v>
       </c>
       <c r="F22">
-        <v>15.5524</v>
+        <v>16.33002</v>
       </c>
       <c r="G22">
         <v>2.29</v>
@@ -3210,28 +3210,28 @@
         <v>7.4</v>
       </c>
       <c r="M22">
-        <v>0.8320534000000001</v>
+        <v>0.87365607</v>
       </c>
       <c r="N22">
-        <v>6.5679466</v>
+        <v>6.52634393</v>
       </c>
       <c r="O22">
-        <v>1.576307184</v>
+        <v>1.5663225432</v>
       </c>
       <c r="P22">
-        <v>4.991639416</v>
+        <v>4.9600213868</v>
       </c>
       <c r="Q22">
-        <v>5.921639416</v>
+        <v>5.8900213868</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.135071207694339</v>
+        <v>0.1359733207387983</v>
       </c>
       <c r="T22">
-        <v>1.50524081067258</v>
+        <v>1.520451732597258</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.893659950190695</v>
+        <v>8.47015233351495</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1159575233836507</v>
+        <v>0.1157260806118302</v>
       </c>
       <c r="C23">
-        <v>66.63186909841139</v>
+        <v>66.12125856694688</v>
       </c>
       <c r="D23">
-        <v>80.67188909841138</v>
+        <v>80.93889856694688</v>
       </c>
       <c r="E23">
-        <v>16.16802</v>
+        <v>16.94564</v>
       </c>
       <c r="F23">
-        <v>16.33002</v>
+        <v>17.10764</v>
       </c>
       <c r="G23">
         <v>2.29</v>
@@ -3292,28 +3292,28 @@
         <v>7.4</v>
       </c>
       <c r="M23">
-        <v>0.87365607</v>
+        <v>0.91525874</v>
       </c>
       <c r="N23">
-        <v>6.52634393</v>
+        <v>6.484741260000001</v>
       </c>
       <c r="O23">
-        <v>1.5663225432</v>
+        <v>1.5563379024</v>
       </c>
       <c r="P23">
-        <v>4.9600213868</v>
+        <v>4.928403357600001</v>
       </c>
       <c r="Q23">
-        <v>5.8900213868</v>
+        <v>5.8584033576</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1359733207387983</v>
+        <v>0.1368985648869617</v>
       </c>
       <c r="T23">
-        <v>1.520451732597258</v>
+        <v>1.53605267816103</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.47015233351495</v>
+        <v>8.085145409264271</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1157260806118302</v>
+        <v>0.1154946378400096</v>
       </c>
       <c r="C24">
-        <v>66.12125856694688</v>
+        <v>65.61242141184</v>
       </c>
       <c r="D24">
-        <v>80.93889856694688</v>
+        <v>81.20768141184</v>
       </c>
       <c r="E24">
-        <v>16.94564</v>
+        <v>17.72326</v>
       </c>
       <c r="F24">
-        <v>17.10764</v>
+        <v>17.88526</v>
       </c>
       <c r="G24">
         <v>2.29</v>
@@ -3374,28 +3374,28 @@
         <v>7.4</v>
       </c>
       <c r="M24">
-        <v>0.91525874</v>
+        <v>0.9568614100000001</v>
       </c>
       <c r="N24">
-        <v>6.484741260000001</v>
+        <v>6.44313859</v>
       </c>
       <c r="O24">
-        <v>1.5563379024</v>
+        <v>1.5463532616</v>
       </c>
       <c r="P24">
-        <v>4.928403357600001</v>
+        <v>4.8967853284</v>
       </c>
       <c r="Q24">
-        <v>5.8584033576</v>
+        <v>5.8267853284</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1368985648869617</v>
+        <v>0.1378478413506619</v>
       </c>
       <c r="T24">
-        <v>1.53605267816103</v>
+        <v>1.552058843090095</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.085145409264271</v>
+        <v>7.73361734799191</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1154946378400096</v>
+        <v>0.1154091150681891</v>
       </c>
       <c r="C25">
-        <v>65.61242141184</v>
+        <v>64.93457435106863</v>
       </c>
       <c r="D25">
-        <v>81.20768141184</v>
+        <v>81.30745435106863</v>
       </c>
       <c r="E25">
-        <v>17.72326</v>
+        <v>18.50088</v>
       </c>
       <c r="F25">
-        <v>17.88526</v>
+        <v>18.66288</v>
       </c>
       <c r="G25">
         <v>2.29</v>
@@ -3456,45 +3456,45 @@
         <v>7.4</v>
       </c>
       <c r="M25">
-        <v>0.9568614100000001</v>
+        <v>1.013394384</v>
       </c>
       <c r="N25">
-        <v>6.44313859</v>
+        <v>6.386605616000001</v>
       </c>
       <c r="O25">
-        <v>1.5463532616</v>
+        <v>1.53278534784</v>
       </c>
       <c r="P25">
-        <v>4.8967853284</v>
+        <v>4.853820268160001</v>
       </c>
       <c r="Q25">
-        <v>5.8267853284</v>
+        <v>5.78382026816</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1378478413506619</v>
+        <v>0.1388220987739331</v>
       </c>
       <c r="T25">
-        <v>1.552058843090095</v>
+        <v>1.568486222885714</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.73361734799191</v>
+        <v>7.302191641117284</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1154091150681891</v>
+        <v>0.1151837522963686</v>
       </c>
       <c r="C26">
-        <v>64.93457435106863</v>
+        <v>64.42104605374796</v>
       </c>
       <c r="D26">
-        <v>81.30745435106863</v>
+        <v>81.57154605374795</v>
       </c>
       <c r="E26">
-        <v>18.50088</v>
+        <v>19.2785</v>
       </c>
       <c r="F26">
-        <v>18.66288</v>
+        <v>19.4405</v>
       </c>
       <c r="G26">
         <v>2.29</v>
@@ -3538,28 +3538,28 @@
         <v>7.4</v>
       </c>
       <c r="M26">
-        <v>1.013394384</v>
+        <v>1.05561915</v>
       </c>
       <c r="N26">
-        <v>6.386605616000001</v>
+        <v>6.34438085</v>
       </c>
       <c r="O26">
-        <v>1.53278534784</v>
+        <v>1.522651404</v>
       </c>
       <c r="P26">
-        <v>4.853820268160001</v>
+        <v>4.821729446</v>
       </c>
       <c r="Q26">
-        <v>5.78382026816</v>
+        <v>5.751729446</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1388220987739331</v>
+        <v>0.1398223363951581</v>
       </c>
       <c r="T26">
-        <v>1.568486222885714</v>
+        <v>1.58535166614255</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.302191641117286</v>
+        <v>7.010103975472593</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1151837522963686</v>
+        <v>0.1149583895245481</v>
       </c>
       <c r="C27">
-        <v>64.42104605374796</v>
+        <v>63.90923891964518</v>
       </c>
       <c r="D27">
-        <v>81.57154605374795</v>
+        <v>81.83735891964517</v>
       </c>
       <c r="E27">
-        <v>19.2785</v>
+        <v>20.05612</v>
       </c>
       <c r="F27">
-        <v>19.4405</v>
+        <v>20.21812</v>
       </c>
       <c r="G27">
         <v>2.29</v>
@@ -3620,28 +3620,28 @@
         <v>7.4</v>
       </c>
       <c r="M27">
-        <v>1.05561915</v>
+        <v>1.097843916</v>
       </c>
       <c r="N27">
-        <v>6.34438085</v>
+        <v>6.302156084</v>
       </c>
       <c r="O27">
-        <v>1.522651404</v>
+        <v>1.51251746016</v>
       </c>
       <c r="P27">
-        <v>4.821729446</v>
+        <v>4.78963862384</v>
       </c>
       <c r="Q27">
-        <v>5.751729446</v>
+        <v>5.71963862384</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1398223363951581</v>
+        <v>0.1408496074656055</v>
       </c>
       <c r="T27">
-        <v>1.58535166614255</v>
+        <v>1.60267293219011</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.010103975472593</v>
+        <v>6.74048459180057</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1149583895245481</v>
+        <v>0.1147330267527276</v>
       </c>
       <c r="C28">
-        <v>63.90923891964518</v>
+        <v>63.39916982975913</v>
       </c>
       <c r="D28">
-        <v>81.83735891964517</v>
+        <v>82.10490982975912</v>
       </c>
       <c r="E28">
-        <v>20.05612</v>
+        <v>20.83374</v>
       </c>
       <c r="F28">
-        <v>20.21812</v>
+        <v>20.99574</v>
       </c>
       <c r="G28">
         <v>2.29</v>
@@ -3702,28 +3702,28 @@
         <v>7.4</v>
       </c>
       <c r="M28">
-        <v>1.097843916</v>
+        <v>1.140068682</v>
       </c>
       <c r="N28">
-        <v>6.302156084</v>
+        <v>6.259931318</v>
       </c>
       <c r="O28">
-        <v>1.51251746016</v>
+        <v>1.50238351632</v>
       </c>
       <c r="P28">
-        <v>4.78963862384</v>
+        <v>4.75754780168</v>
       </c>
       <c r="Q28">
-        <v>5.71963862384</v>
+        <v>5.68754780168</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1408496074656055</v>
+        <v>0.1419050229489419</v>
       </c>
       <c r="T28">
-        <v>1.60267293219011</v>
+        <v>1.620468753471851</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.74048459180057</v>
+        <v>6.490837014326475</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1147330267527276</v>
+        <v>0.114507663980907</v>
       </c>
       <c r="C29">
-        <v>63.39916982975913</v>
+        <v>62.89085588656889</v>
       </c>
       <c r="D29">
-        <v>82.10490982975912</v>
+        <v>82.37421588656889</v>
       </c>
       <c r="E29">
-        <v>20.83374</v>
+        <v>21.61136</v>
       </c>
       <c r="F29">
-        <v>20.99574</v>
+        <v>21.77336</v>
       </c>
       <c r="G29">
         <v>2.29</v>
@@ -3784,28 +3784,28 @@
         <v>7.4</v>
       </c>
       <c r="M29">
-        <v>1.140068682</v>
+        <v>1.182293448</v>
       </c>
       <c r="N29">
-        <v>6.259931318</v>
+        <v>6.217706552</v>
       </c>
       <c r="O29">
-        <v>1.50238351632</v>
+        <v>1.49224957248</v>
       </c>
       <c r="P29">
-        <v>4.75754780168</v>
+        <v>4.725456979520001</v>
       </c>
       <c r="Q29">
-        <v>5.68754780168</v>
+        <v>5.65545697952</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1419050229489419</v>
+        <v>0.1429897555290376</v>
       </c>
       <c r="T29">
-        <v>1.620468753471851</v>
+        <v>1.638758903122529</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.490837014326475</v>
+        <v>6.259021406671957</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.114507663980907</v>
+        <v>0.1145027012090865</v>
       </c>
       <c r="C30">
-        <v>62.89085588656889</v>
+        <v>62.1191862266595</v>
       </c>
       <c r="D30">
-        <v>82.37421588656889</v>
+        <v>82.3801662266595</v>
       </c>
       <c r="E30">
-        <v>21.61136</v>
+        <v>22.38898</v>
       </c>
       <c r="F30">
-        <v>21.77336</v>
+        <v>22.55098</v>
       </c>
       <c r="G30">
         <v>2.29</v>
@@ -3866,45 +3866,45 @@
         <v>7.4</v>
       </c>
       <c r="M30">
-        <v>1.182293448</v>
+        <v>1.247069194</v>
       </c>
       <c r="N30">
-        <v>6.217706552</v>
+        <v>6.152930806000001</v>
       </c>
       <c r="O30">
-        <v>1.49224957248</v>
+        <v>1.47670339344</v>
       </c>
       <c r="P30">
-        <v>4.725456979520001</v>
+        <v>4.67622741256</v>
       </c>
       <c r="Q30">
-        <v>5.65545697952</v>
+        <v>5.60622741256</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1429897555290376</v>
+        <v>0.1441050439564599</v>
       </c>
       <c r="T30">
-        <v>1.638758903122529</v>
+        <v>1.657564268256325</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.259021406671957</v>
+        <v>5.933912918066998</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1145027012090865</v>
+        <v>0.114284938437266</v>
       </c>
       <c r="C31">
-        <v>62.11918622665951</v>
+        <v>61.6035119004077</v>
       </c>
       <c r="D31">
-        <v>82.3801662266595</v>
+        <v>82.64211190040768</v>
       </c>
       <c r="E31">
-        <v>22.38898</v>
+        <v>23.1666</v>
       </c>
       <c r="F31">
-        <v>22.55098</v>
+        <v>23.3286</v>
       </c>
       <c r="G31">
         <v>2.29</v>
@@ -3948,28 +3948,28 @@
         <v>7.4</v>
       </c>
       <c r="M31">
-        <v>1.247069194</v>
+        <v>1.29007158</v>
       </c>
       <c r="N31">
-        <v>6.152930806000001</v>
+        <v>6.10992842</v>
       </c>
       <c r="O31">
-        <v>1.47670339344</v>
+        <v>1.4663828208</v>
       </c>
       <c r="P31">
-        <v>4.67622741256</v>
+        <v>4.6435455992</v>
       </c>
       <c r="Q31">
-        <v>5.60622741256</v>
+        <v>5.5735455992</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1441050439564599</v>
+        <v>0.1452521977675229</v>
       </c>
       <c r="T31">
-        <v>1.657564268256325</v>
+        <v>1.6769069295368</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.933912918066999</v>
+        <v>5.736115820798099</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.114284938437266</v>
+        <v>0.1140671756654455</v>
       </c>
       <c r="C32">
-        <v>61.6035119004077</v>
+        <v>61.08950871450777</v>
       </c>
       <c r="D32">
-        <v>82.64211190040768</v>
+        <v>82.90572871450776</v>
       </c>
       <c r="E32">
-        <v>23.1666</v>
+        <v>23.94422</v>
       </c>
       <c r="F32">
-        <v>23.3286</v>
+        <v>24.10622</v>
       </c>
       <c r="G32">
         <v>2.29</v>
@@ -4030,28 +4030,28 @@
         <v>7.4</v>
       </c>
       <c r="M32">
-        <v>1.29007158</v>
+        <v>1.333073966</v>
       </c>
       <c r="N32">
-        <v>6.10992842</v>
+        <v>6.066926034</v>
       </c>
       <c r="O32">
-        <v>1.4663828208</v>
+        <v>1.45606224816</v>
       </c>
       <c r="P32">
-        <v>4.6435455992</v>
+        <v>4.610863785839999</v>
       </c>
       <c r="Q32">
-        <v>5.5735455992</v>
+        <v>5.540863785839999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1452521977675229</v>
+        <v>0.1464326024136891</v>
       </c>
       <c r="T32">
-        <v>1.6769069295368</v>
+        <v>1.696810247665985</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.736115820798099</v>
+        <v>5.551079826578804</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1140671756654455</v>
+        <v>0.113849412893625</v>
       </c>
       <c r="C33">
-        <v>61.08950871450777</v>
+        <v>60.57719271224972</v>
       </c>
       <c r="D33">
-        <v>82.90572871450776</v>
+        <v>83.17103271224971</v>
       </c>
       <c r="E33">
-        <v>23.94422</v>
+        <v>24.72184</v>
       </c>
       <c r="F33">
-        <v>24.10622</v>
+        <v>24.88384</v>
       </c>
       <c r="G33">
         <v>2.29</v>
@@ -4112,28 +4112,28 @@
         <v>7.4</v>
       </c>
       <c r="M33">
-        <v>1.333073966</v>
+        <v>1.376076352</v>
       </c>
       <c r="N33">
-        <v>6.066926034</v>
+        <v>6.023923648</v>
       </c>
       <c r="O33">
-        <v>1.45606224816</v>
+        <v>1.44574167552</v>
       </c>
       <c r="P33">
-        <v>4.610863785839999</v>
+        <v>4.57818197248</v>
       </c>
       <c r="Q33">
-        <v>5.540863785839999</v>
+        <v>5.50818197248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1464326024136891</v>
+        <v>0.1476477248435662</v>
       </c>
       <c r="T33">
-        <v>1.696810247665985</v>
+        <v>1.717298957504852</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.551079826578804</v>
+        <v>5.377608581998217</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.113849412893625</v>
+        <v>0.1136316501218045</v>
       </c>
       <c r="C34">
-        <v>60.57719271224972</v>
+        <v>60.06658014294131</v>
       </c>
       <c r="D34">
-        <v>83.17103271224971</v>
+        <v>83.4380401429413</v>
       </c>
       <c r="E34">
-        <v>24.72184</v>
+        <v>25.49946</v>
       </c>
       <c r="F34">
-        <v>24.88384</v>
+        <v>25.66146</v>
       </c>
       <c r="G34">
         <v>2.29</v>
@@ -4194,28 +4194,28 @@
         <v>7.4</v>
       </c>
       <c r="M34">
-        <v>1.376076352</v>
+        <v>1.419078738</v>
       </c>
       <c r="N34">
-        <v>6.023923648</v>
+        <v>5.980921262000001</v>
       </c>
       <c r="O34">
-        <v>1.44574167552</v>
+        <v>1.43542110288</v>
       </c>
       <c r="P34">
-        <v>4.57818197248</v>
+        <v>4.54550015912</v>
       </c>
       <c r="Q34">
-        <v>5.50818197248</v>
+        <v>5.47550015912</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1476477248435662</v>
+        <v>0.1488991195847828</v>
       </c>
       <c r="T34">
-        <v>1.717298957504852</v>
+        <v>1.738399270622491</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.377608581998217</v>
+        <v>5.21465074618009</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1136316501218045</v>
+        <v>0.1134138873499839</v>
       </c>
       <c r="C35">
-        <v>60.06658014294131</v>
+        <v>59.55768746522568</v>
       </c>
       <c r="D35">
-        <v>83.4380401429413</v>
+        <v>83.70676746522568</v>
       </c>
       <c r="E35">
-        <v>25.49946</v>
+        <v>26.27708</v>
       </c>
       <c r="F35">
-        <v>25.66146</v>
+        <v>26.43908</v>
       </c>
       <c r="G35">
         <v>2.29</v>
@@ -4276,28 +4276,28 @@
         <v>7.4</v>
       </c>
       <c r="M35">
-        <v>1.419078738</v>
+        <v>1.462081124</v>
       </c>
       <c r="N35">
-        <v>5.980921262000001</v>
+        <v>5.937918876</v>
       </c>
       <c r="O35">
-        <v>1.43542110288</v>
+        <v>1.42510053024</v>
       </c>
       <c r="P35">
-        <v>4.54550015912</v>
+        <v>4.51281834576</v>
       </c>
       <c r="Q35">
-        <v>5.47550015912</v>
+        <v>5.44281834576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1488991195847828</v>
+        <v>0.1501884353787636</v>
       </c>
       <c r="T35">
-        <v>1.738399270622491</v>
+        <v>1.760138987167937</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.21465074618009</v>
+        <v>5.061278665410088</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1134138873499839</v>
+        <v>0.1131961245781634</v>
       </c>
       <c r="C36">
-        <v>59.55768746522568</v>
+        <v>59.05053135046323</v>
       </c>
       <c r="D36">
-        <v>83.70676746522568</v>
+        <v>83.97723135046323</v>
       </c>
       <c r="E36">
-        <v>26.27708</v>
+        <v>27.0547</v>
       </c>
       <c r="F36">
-        <v>26.43908</v>
+        <v>27.2167</v>
       </c>
       <c r="G36">
         <v>2.29</v>
@@ -4358,28 +4358,28 @@
         <v>7.4</v>
       </c>
       <c r="M36">
-        <v>1.462081124</v>
+        <v>1.50508351</v>
       </c>
       <c r="N36">
-        <v>5.937918876</v>
+        <v>5.89491649</v>
       </c>
       <c r="O36">
-        <v>1.42510053024</v>
+        <v>1.4147799576</v>
       </c>
       <c r="P36">
-        <v>4.51281834576</v>
+        <v>4.4801365324</v>
       </c>
       <c r="Q36">
-        <v>5.44281834576</v>
+        <v>5.410136532399999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1501884353787636</v>
+        <v>0.1515174224279437</v>
       </c>
       <c r="T36">
-        <v>1.760138987167937</v>
+        <v>1.782547618068628</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.061278665410088</v>
+        <v>4.916670703541227</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1131961245781634</v>
+        <v>0.1129783618063429</v>
       </c>
       <c r="C37">
-        <v>59.05053135046323</v>
+        <v>58.54512868617925</v>
       </c>
       <c r="D37">
-        <v>83.97723135046323</v>
+        <v>84.24944868617925</v>
       </c>
       <c r="E37">
-        <v>27.0547</v>
+        <v>27.83232</v>
       </c>
       <c r="F37">
-        <v>27.2167</v>
+        <v>27.99432</v>
       </c>
       <c r="G37">
         <v>2.29</v>
@@ -4440,28 +4440,28 @@
         <v>7.4</v>
       </c>
       <c r="M37">
-        <v>1.50508351</v>
+        <v>1.548085896</v>
       </c>
       <c r="N37">
-        <v>5.89491649</v>
+        <v>5.851914104</v>
       </c>
       <c r="O37">
-        <v>1.4147799576</v>
+        <v>1.40445938496</v>
       </c>
       <c r="P37">
-        <v>4.4801365324</v>
+        <v>4.44745471904</v>
       </c>
       <c r="Q37">
-        <v>5.410136532399999</v>
+        <v>5.37745471904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1515174224279437</v>
+        <v>0.1528879403224108</v>
       </c>
       <c r="T37">
-        <v>1.782547618068628</v>
+        <v>1.805656518684965</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.916670703541227</v>
+        <v>4.780096517331749</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1129783618063429</v>
+        <v>0.1127605990345224</v>
       </c>
       <c r="C38">
-        <v>58.54512868617923</v>
+        <v>58.04149657957896</v>
       </c>
       <c r="D38">
-        <v>84.24944868617922</v>
+        <v>84.52343657957896</v>
       </c>
       <c r="E38">
-        <v>27.83232</v>
+        <v>28.60994</v>
       </c>
       <c r="F38">
-        <v>27.99432</v>
+        <v>28.77194</v>
       </c>
       <c r="G38">
         <v>2.29</v>
@@ -4522,28 +4522,28 @@
         <v>7.4</v>
       </c>
       <c r="M38">
-        <v>1.548085896</v>
+        <v>1.591088282</v>
       </c>
       <c r="N38">
-        <v>5.851914104</v>
+        <v>5.808911718</v>
       </c>
       <c r="O38">
-        <v>1.40445938496</v>
+        <v>1.39413881232</v>
       </c>
       <c r="P38">
-        <v>4.44745471904</v>
+        <v>4.41477290568</v>
       </c>
       <c r="Q38">
-        <v>5.37745471904</v>
+        <v>5.344772905679999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1528879403224108</v>
+        <v>0.1543019667214641</v>
       </c>
       <c r="T38">
-        <v>1.805656518684965</v>
+        <v>1.829499035193884</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.780096517331749</v>
+        <v>4.650904719566026</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1127605990345224</v>
+        <v>0.1125428362627019</v>
       </c>
       <c r="C39">
-        <v>58.04149657957896</v>
+        <v>57.53965236113127</v>
       </c>
       <c r="D39">
-        <v>84.52343657957896</v>
+        <v>84.79921236113127</v>
       </c>
       <c r="E39">
-        <v>28.60994</v>
+        <v>29.38756</v>
       </c>
       <c r="F39">
-        <v>28.77194</v>
+        <v>29.54956</v>
       </c>
       <c r="G39">
         <v>2.29</v>
@@ -4604,28 +4604,28 @@
         <v>7.4</v>
       </c>
       <c r="M39">
-        <v>1.591088282</v>
+        <v>1.634090668</v>
       </c>
       <c r="N39">
-        <v>5.808911718</v>
+        <v>5.765909332000001</v>
       </c>
       <c r="O39">
-        <v>1.39413881232</v>
+        <v>1.38381823968</v>
       </c>
       <c r="P39">
-        <v>4.41477290568</v>
+        <v>4.38209109232</v>
       </c>
       <c r="Q39">
-        <v>5.344772905679999</v>
+        <v>5.31209109232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1543019667214641</v>
+        <v>0.1557616068753256</v>
       </c>
       <c r="T39">
-        <v>1.829499035193884</v>
+        <v>1.854110665138575</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.650904719566026</v>
+        <v>4.528512490103763</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1125428362627019</v>
+        <v>0.1130660734908814</v>
       </c>
       <c r="C40">
-        <v>57.53965236113127</v>
+        <v>56.10241150733405</v>
       </c>
       <c r="D40">
-        <v>84.79921236113127</v>
+        <v>84.13959150733405</v>
       </c>
       <c r="E40">
-        <v>29.38756</v>
+        <v>30.16518</v>
       </c>
       <c r="F40">
-        <v>29.54956</v>
+        <v>30.32718</v>
       </c>
       <c r="G40">
         <v>2.29</v>
@@ -4686,45 +4686,45 @@
         <v>7.4</v>
       </c>
       <c r="M40">
-        <v>1.634090668</v>
+        <v>1.752911004</v>
       </c>
       <c r="N40">
-        <v>5.765909332000001</v>
+        <v>5.647088996</v>
       </c>
       <c r="O40">
-        <v>1.38381823968</v>
+        <v>1.35530135904</v>
       </c>
       <c r="P40">
-        <v>4.38209109232</v>
+        <v>4.291787636960001</v>
       </c>
       <c r="Q40">
-        <v>5.31209109232</v>
+        <v>5.22178763696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1557616068753256</v>
+        <v>0.1572691040834121</v>
       </c>
       <c r="T40">
-        <v>1.854110665138575</v>
+        <v>1.879529233769978</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.528512490103763</v>
+        <v>4.22154917341143</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1130660734908814</v>
+        <v>0.1128673107190609</v>
       </c>
       <c r="C41">
-        <v>56.10241150733405</v>
+        <v>55.57415022245978</v>
       </c>
       <c r="D41">
-        <v>84.13959150733405</v>
+        <v>84.38895022245977</v>
       </c>
       <c r="E41">
-        <v>30.16518</v>
+        <v>30.9428</v>
       </c>
       <c r="F41">
-        <v>30.32718</v>
+        <v>31.1048</v>
       </c>
       <c r="G41">
         <v>2.29</v>
@@ -4768,28 +4768,28 @@
         <v>7.4</v>
       </c>
       <c r="M41">
-        <v>1.752911004</v>
+        <v>1.79785744</v>
       </c>
       <c r="N41">
-        <v>5.647088996</v>
+        <v>5.60214256</v>
       </c>
       <c r="O41">
-        <v>1.35530135904</v>
+        <v>1.3445142144</v>
       </c>
       <c r="P41">
-        <v>4.291787636960001</v>
+        <v>4.2576283456</v>
       </c>
       <c r="Q41">
-        <v>5.22178763696</v>
+        <v>5.187628345599999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1572691040834121</v>
+        <v>0.1588268511984348</v>
       </c>
       <c r="T41">
-        <v>1.879529233769978</v>
+        <v>1.905795088022427</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.22154917341143</v>
+        <v>4.116010444076144</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1128673107190609</v>
+        <v>0.1126685479472403</v>
       </c>
       <c r="C42">
-        <v>55.57415022245978</v>
+        <v>55.04737134541154</v>
       </c>
       <c r="D42">
-        <v>84.38895022245977</v>
+        <v>84.63979134541154</v>
       </c>
       <c r="E42">
-        <v>30.9428</v>
+        <v>31.72042</v>
       </c>
       <c r="F42">
-        <v>31.1048</v>
+        <v>31.88242</v>
       </c>
       <c r="G42">
         <v>2.29</v>
@@ -4850,28 +4850,28 @@
         <v>7.4</v>
       </c>
       <c r="M42">
-        <v>1.79785744</v>
+        <v>1.842803876</v>
       </c>
       <c r="N42">
-        <v>5.60214256</v>
+        <v>5.557196124</v>
       </c>
       <c r="O42">
-        <v>1.3445142144</v>
+        <v>1.33372706976</v>
       </c>
       <c r="P42">
-        <v>4.2576283456</v>
+        <v>4.22346905424</v>
       </c>
       <c r="Q42">
-        <v>5.187628345599999</v>
+        <v>5.153469054239999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1588268511984348</v>
+        <v>0.1604374033004074</v>
       </c>
       <c r="T42">
-        <v>1.905795088022427</v>
+        <v>1.932951310215636</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.116010444076144</v>
+        <v>4.01561994544014</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1126685479472403</v>
+        <v>0.1135869851754198</v>
       </c>
       <c r="C43">
-        <v>55.04737134541154</v>
+        <v>53.12297759296036</v>
       </c>
       <c r="D43">
-        <v>84.63979134541154</v>
+        <v>83.49301759296036</v>
       </c>
       <c r="E43">
-        <v>31.72042</v>
+        <v>32.49804</v>
       </c>
       <c r="F43">
-        <v>31.88242</v>
+        <v>32.66004</v>
       </c>
       <c r="G43">
         <v>2.29</v>
@@ -4932,45 +4932,45 @@
         <v>7.4</v>
       </c>
       <c r="M43">
-        <v>1.842803876</v>
+        <v>2.002060452</v>
       </c>
       <c r="N43">
-        <v>5.557196124</v>
+        <v>5.397939548</v>
       </c>
       <c r="O43">
-        <v>1.33372706976</v>
+        <v>1.29550549152</v>
       </c>
       <c r="P43">
-        <v>4.22346905424</v>
+        <v>4.10243405648</v>
       </c>
       <c r="Q43">
-        <v>5.153469054239999</v>
+        <v>5.03243405648</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1604374033004074</v>
+        <v>0.1621034916817583</v>
       </c>
       <c r="T43">
-        <v>1.932951310215636</v>
+        <v>1.961043953863785</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.01561994544014</v>
+        <v>3.696192086811172</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1135869851754198</v>
+        <v>0.1134148224035993</v>
       </c>
       <c r="C44">
-        <v>53.12297759296035</v>
+        <v>52.55794987414186</v>
       </c>
       <c r="D44">
-        <v>83.49301759296034</v>
+        <v>83.70560987414186</v>
       </c>
       <c r="E44">
-        <v>32.49804</v>
+        <v>33.27566</v>
       </c>
       <c r="F44">
-        <v>32.66004</v>
+        <v>33.43766</v>
       </c>
       <c r="G44">
         <v>2.29</v>
@@ -5014,28 +5014,28 @@
         <v>7.4</v>
       </c>
       <c r="M44">
-        <v>2.002060452</v>
+        <v>2.049728558</v>
       </c>
       <c r="N44">
-        <v>5.397939548</v>
+        <v>5.350271442</v>
       </c>
       <c r="O44">
-        <v>1.29550549152</v>
+        <v>1.28406514608</v>
       </c>
       <c r="P44">
-        <v>4.10243405648</v>
+        <v>4.066206295920001</v>
       </c>
       <c r="Q44">
-        <v>5.03243405648</v>
+        <v>4.99620629592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1621034916817583</v>
+        <v>0.1638280393045602</v>
       </c>
       <c r="T44">
-        <v>1.961043953863784</v>
+        <v>1.990122304306605</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.696192086811172</v>
+        <v>3.610234131303936</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1134148224035993</v>
+        <v>0.1132426596317788</v>
       </c>
       <c r="C45">
-        <v>52.55794987414186</v>
+        <v>51.99400753589983</v>
       </c>
       <c r="D45">
-        <v>83.70560987414186</v>
+        <v>83.91928753589983</v>
       </c>
       <c r="E45">
-        <v>33.27566</v>
+        <v>34.05328</v>
       </c>
       <c r="F45">
-        <v>33.43766</v>
+        <v>34.21528</v>
       </c>
       <c r="G45">
         <v>2.29</v>
@@ -5096,28 +5096,28 @@
         <v>7.4</v>
       </c>
       <c r="M45">
-        <v>2.049728558</v>
+        <v>2.097396664</v>
       </c>
       <c r="N45">
-        <v>5.350271442</v>
+        <v>5.302603336000001</v>
       </c>
       <c r="O45">
-        <v>1.28406514608</v>
+        <v>1.27262480064</v>
       </c>
       <c r="P45">
-        <v>4.066206295920001</v>
+        <v>4.029978535360001</v>
       </c>
       <c r="Q45">
-        <v>4.99620629592</v>
+        <v>4.95997853536</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1638280393045602</v>
+        <v>0.1656141779138907</v>
       </c>
       <c r="T45">
-        <v>1.990122304306605</v>
+        <v>2.02023916726524</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.610234131303936</v>
+        <v>3.528183355592483</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1132426596317788</v>
+        <v>0.1140280968599583</v>
       </c>
       <c r="C46">
-        <v>51.99400753589983</v>
+        <v>50.25031438383341</v>
       </c>
       <c r="D46">
-        <v>83.91928753589983</v>
+        <v>82.9532143838334</v>
       </c>
       <c r="E46">
-        <v>34.05328</v>
+        <v>34.8309</v>
       </c>
       <c r="F46">
-        <v>34.21528</v>
+        <v>34.9929</v>
       </c>
       <c r="G46">
         <v>2.29</v>
@@ -5178,45 +5178,45 @@
         <v>7.4</v>
       </c>
       <c r="M46">
-        <v>2.097396664</v>
+        <v>2.24304489</v>
       </c>
       <c r="N46">
-        <v>5.302603336000001</v>
+        <v>5.15695511</v>
       </c>
       <c r="O46">
-        <v>1.27262480064</v>
+        <v>1.2376692264</v>
       </c>
       <c r="P46">
-        <v>4.029978535360001</v>
+        <v>3.9192858836</v>
       </c>
       <c r="Q46">
-        <v>4.95997853536</v>
+        <v>4.8492858836</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1656141779138907</v>
+        <v>0.167465267018106</v>
       </c>
       <c r="T46">
-        <v>2.02023916726524</v>
+        <v>2.051451188876916</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.528183355592483</v>
+        <v>3.299086894333176</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1140280968599583</v>
+        <v>0.1138772140881378</v>
       </c>
       <c r="C47">
-        <v>50.25031438383341</v>
+        <v>49.65654754359178</v>
       </c>
       <c r="D47">
-        <v>82.9532143838334</v>
+        <v>83.13706754359178</v>
       </c>
       <c r="E47">
-        <v>34.8309</v>
+        <v>35.60852000000001</v>
       </c>
       <c r="F47">
-        <v>34.9929</v>
+        <v>35.77052</v>
       </c>
       <c r="G47">
         <v>2.29</v>
@@ -5260,28 +5260,28 @@
         <v>7.4</v>
       </c>
       <c r="M47">
-        <v>2.24304489</v>
+        <v>2.292890332</v>
       </c>
       <c r="N47">
-        <v>5.15695511</v>
+        <v>5.107109668</v>
       </c>
       <c r="O47">
-        <v>1.2376692264</v>
+        <v>1.22570632032</v>
       </c>
       <c r="P47">
-        <v>3.9192858836</v>
+        <v>3.88140334768</v>
       </c>
       <c r="Q47">
-        <v>4.8492858836</v>
+        <v>4.81140334768</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.167465267018106</v>
+        <v>0.1693849149780329</v>
       </c>
       <c r="T47">
-        <v>2.051451188876916</v>
+        <v>2.083819211289025</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.299086894333176</v>
+        <v>3.227367614021585</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1138772140881378</v>
+        <v>0.1137263313163173</v>
       </c>
       <c r="C48">
-        <v>49.65654754359178</v>
+        <v>49.06359747863648</v>
       </c>
       <c r="D48">
-        <v>83.13706754359178</v>
+        <v>83.32173747863648</v>
       </c>
       <c r="E48">
-        <v>35.60852000000001</v>
+        <v>36.38614</v>
       </c>
       <c r="F48">
-        <v>35.77052</v>
+        <v>36.54814</v>
       </c>
       <c r="G48">
         <v>2.29</v>
@@ -5342,28 +5342,28 @@
         <v>7.4</v>
       </c>
       <c r="M48">
-        <v>2.292890332</v>
+        <v>2.342735774</v>
       </c>
       <c r="N48">
-        <v>5.107109668</v>
+        <v>5.057264226</v>
       </c>
       <c r="O48">
-        <v>1.22570632032</v>
+        <v>1.21374341424</v>
       </c>
       <c r="P48">
-        <v>3.88140334768</v>
+        <v>3.84352081176</v>
       </c>
       <c r="Q48">
-        <v>4.81140334768</v>
+        <v>4.77352081176</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1693849149780329</v>
+        <v>0.1713770024836175</v>
       </c>
       <c r="T48">
-        <v>2.083819211289025</v>
+        <v>2.117408668509138</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.227367614021585</v>
+        <v>3.158700217978572</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1137263313163173</v>
+        <v>0.1135754485444967</v>
       </c>
       <c r="C49">
-        <v>49.06359747863648</v>
+        <v>48.47146964392145</v>
       </c>
       <c r="D49">
-        <v>83.32173747863648</v>
+        <v>83.50722964392145</v>
       </c>
       <c r="E49">
-        <v>36.38614</v>
+        <v>37.16376</v>
       </c>
       <c r="F49">
-        <v>36.54814</v>
+        <v>37.32576</v>
       </c>
       <c r="G49">
         <v>2.29</v>
@@ -5424,28 +5424,28 @@
         <v>7.4</v>
       </c>
       <c r="M49">
-        <v>2.342735774</v>
+        <v>2.392581216</v>
       </c>
       <c r="N49">
-        <v>5.057264226</v>
+        <v>5.007418784</v>
       </c>
       <c r="O49">
-        <v>1.21374341424</v>
+        <v>1.20178050816</v>
       </c>
       <c r="P49">
-        <v>3.84352081176</v>
+        <v>3.80563827584</v>
       </c>
       <c r="Q49">
-        <v>4.77352081176</v>
+        <v>4.73563827584</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1713770024836175</v>
+        <v>0.1734457087394168</v>
       </c>
       <c r="T49">
-        <v>2.117408668509138</v>
+        <v>2.152290027930024</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.158700217978572</v>
+        <v>3.092893963437352</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1135754485444967</v>
+        <v>0.1134245657726762</v>
       </c>
       <c r="C50">
-        <v>48.47146964392146</v>
+        <v>47.88016954308476</v>
       </c>
       <c r="D50">
-        <v>83.50722964392145</v>
+        <v>83.69354954308476</v>
       </c>
       <c r="E50">
-        <v>37.16376</v>
+        <v>37.94138</v>
       </c>
       <c r="F50">
-        <v>37.32576</v>
+        <v>38.10338</v>
       </c>
       <c r="G50">
         <v>2.29</v>
@@ -5506,28 +5506,28 @@
         <v>7.4</v>
       </c>
       <c r="M50">
-        <v>2.392581216</v>
+        <v>2.442426658</v>
       </c>
       <c r="N50">
-        <v>5.007418784</v>
+        <v>4.957573342</v>
       </c>
       <c r="O50">
-        <v>1.20178050816</v>
+        <v>1.18981760208</v>
       </c>
       <c r="P50">
-        <v>3.80563827584</v>
+        <v>3.76775573992</v>
       </c>
       <c r="Q50">
-        <v>4.73563827584</v>
+        <v>4.69775573992</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1734457087394168</v>
+        <v>0.1755955407307377</v>
       </c>
       <c r="T50">
-        <v>2.152290027930024</v>
+        <v>2.188539283798788</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.092893963437353</v>
+        <v>3.029773678469243</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1134245657726762</v>
+        <v>0.1162376830008557</v>
       </c>
       <c r="C51">
-        <v>47.88016954308476</v>
+        <v>43.76002383700374</v>
       </c>
       <c r="D51">
-        <v>83.69354954308476</v>
+        <v>80.35102383700374</v>
       </c>
       <c r="E51">
-        <v>37.94138</v>
+        <v>38.719</v>
       </c>
       <c r="F51">
-        <v>38.10338</v>
+        <v>38.881</v>
       </c>
       <c r="G51">
         <v>2.29</v>
@@ -5588,45 +5588,45 @@
         <v>7.4</v>
       </c>
       <c r="M51">
-        <v>2.442426658</v>
+        <v>2.7955439</v>
       </c>
       <c r="N51">
-        <v>4.957573342</v>
+        <v>4.6044561</v>
       </c>
       <c r="O51">
-        <v>1.18981760208</v>
+        <v>1.105069464</v>
       </c>
       <c r="P51">
-        <v>3.76775573992</v>
+        <v>3.499386636</v>
       </c>
       <c r="Q51">
-        <v>4.69775573992</v>
+        <v>4.429386636</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1755955407307377</v>
+        <v>0.1778313660017114</v>
       </c>
       <c r="T51">
-        <v>2.188539283798788</v>
+        <v>2.226238509902303</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.029773678469243</v>
+        <v>2.647069860001126</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1162376830008557</v>
+        <v>0.1161460802290352</v>
       </c>
       <c r="C52">
-        <v>43.76002383700374</v>
+        <v>43.08703477703794</v>
       </c>
       <c r="D52">
-        <v>80.35102383700374</v>
+        <v>80.45565477703794</v>
       </c>
       <c r="E52">
-        <v>38.719</v>
+        <v>39.49662</v>
       </c>
       <c r="F52">
-        <v>38.881</v>
+        <v>39.65862</v>
       </c>
       <c r="G52">
         <v>2.29</v>
@@ -5670,28 +5670,28 @@
         <v>7.4</v>
       </c>
       <c r="M52">
-        <v>2.7955439</v>
+        <v>2.851454778</v>
       </c>
       <c r="N52">
-        <v>4.6044561</v>
+        <v>4.548545222</v>
       </c>
       <c r="O52">
-        <v>1.105069464</v>
+        <v>1.09165085328</v>
       </c>
       <c r="P52">
-        <v>3.499386636</v>
+        <v>3.45689436872</v>
       </c>
       <c r="Q52">
-        <v>4.429386636</v>
+        <v>4.386894368719999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1778313660017114</v>
+        <v>0.1801584494470106</v>
       </c>
       <c r="T52">
-        <v>2.226238509902303</v>
+        <v>2.265476479928411</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.647069860001126</v>
+        <v>2.595166529412868</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1161460802290352</v>
+        <v>0.1160544774572147</v>
       </c>
       <c r="C53">
-        <v>43.08703477703794</v>
+        <v>42.4143185675572</v>
       </c>
       <c r="D53">
-        <v>80.45565477703794</v>
+        <v>80.56055856755719</v>
       </c>
       <c r="E53">
-        <v>39.49662</v>
+        <v>40.27424000000001</v>
       </c>
       <c r="F53">
-        <v>39.65862</v>
+        <v>40.43624000000001</v>
       </c>
       <c r="G53">
         <v>2.29</v>
@@ -5752,28 +5752,28 @@
         <v>7.4</v>
       </c>
       <c r="M53">
-        <v>2.851454778</v>
+        <v>2.907365656000001</v>
       </c>
       <c r="N53">
-        <v>4.548545222</v>
+        <v>4.492634344</v>
       </c>
       <c r="O53">
-        <v>1.09165085328</v>
+        <v>1.07823224256</v>
       </c>
       <c r="P53">
-        <v>3.45689436872</v>
+        <v>3.41440210144</v>
       </c>
       <c r="Q53">
-        <v>4.386894368719999</v>
+        <v>4.34440210144</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1801584494470106</v>
+        <v>0.1825824947025306</v>
       </c>
       <c r="T53">
-        <v>2.265476479928411</v>
+        <v>2.306349365372273</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.595166529412868</v>
+        <v>2.545259480770313</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1160544774572147</v>
+        <v>0.1175337946853942</v>
       </c>
       <c r="C54">
-        <v>42.4143185675572</v>
+        <v>39.97535299503566</v>
       </c>
       <c r="D54">
-        <v>80.56055856755719</v>
+        <v>78.89921299503565</v>
       </c>
       <c r="E54">
-        <v>40.27424000000001</v>
+        <v>41.05186</v>
       </c>
       <c r="F54">
-        <v>40.43624000000001</v>
+        <v>41.21386</v>
       </c>
       <c r="G54">
         <v>2.29</v>
@@ -5834,45 +5834,45 @@
         <v>7.4</v>
       </c>
       <c r="M54">
-        <v>2.907365656000001</v>
+        <v>3.124010588</v>
       </c>
       <c r="N54">
-        <v>4.492634344</v>
+        <v>4.275989411999999</v>
       </c>
       <c r="O54">
-        <v>1.07823224256</v>
+        <v>1.02623745888</v>
       </c>
       <c r="P54">
-        <v>3.41440210144</v>
+        <v>3.24975195312</v>
       </c>
       <c r="Q54">
-        <v>4.34440210144</v>
+        <v>4.179751953119999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1825824947025306</v>
+        <v>0.1851096908199876</v>
       </c>
       <c r="T54">
-        <v>2.306349365372273</v>
+        <v>2.34896152253715</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.545259480770313</v>
+        <v>2.368749974287859</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1175337946853942</v>
+        <v>0.1174718319135736</v>
       </c>
       <c r="C55">
-        <v>39.97535299503566</v>
+        <v>39.26594408719142</v>
       </c>
       <c r="D55">
-        <v>78.89921299503565</v>
+        <v>78.96742408719142</v>
       </c>
       <c r="E55">
-        <v>41.05186</v>
+        <v>41.82948</v>
       </c>
       <c r="F55">
-        <v>41.21386</v>
+        <v>41.99148</v>
       </c>
       <c r="G55">
         <v>2.29</v>
@@ -5916,28 +5916,28 @@
         <v>7.4</v>
       </c>
       <c r="M55">
-        <v>3.124010588</v>
+        <v>3.182954184000001</v>
       </c>
       <c r="N55">
-        <v>4.275989411999999</v>
+        <v>4.217045816</v>
       </c>
       <c r="O55">
-        <v>1.02623745888</v>
+        <v>1.01209099584</v>
       </c>
       <c r="P55">
-        <v>3.24975195312</v>
+        <v>3.20495482016</v>
       </c>
       <c r="Q55">
-        <v>4.179751953119999</v>
+        <v>4.134954820159999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1851096908199876</v>
+        <v>0.1877467650295079</v>
       </c>
       <c r="T55">
-        <v>2.34896152253715</v>
+        <v>2.393426382187457</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.368749974287859</v>
+        <v>2.324884234023269</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1174718319135736</v>
+        <v>0.1174098691417531</v>
       </c>
       <c r="C56">
-        <v>39.26594408719142</v>
+        <v>38.55665322308584</v>
       </c>
       <c r="D56">
-        <v>78.96742408719142</v>
+        <v>79.03575322308583</v>
       </c>
       <c r="E56">
-        <v>41.82948</v>
+        <v>42.6071</v>
       </c>
       <c r="F56">
-        <v>41.99148</v>
+        <v>42.7691</v>
       </c>
       <c r="G56">
         <v>2.29</v>
@@ -5998,28 +5998,28 @@
         <v>7.4</v>
       </c>
       <c r="M56">
-        <v>3.182954184000001</v>
+        <v>3.24189778</v>
       </c>
       <c r="N56">
-        <v>4.217045816</v>
+        <v>4.15810222</v>
       </c>
       <c r="O56">
-        <v>1.01209099584</v>
+        <v>0.9979445328</v>
       </c>
       <c r="P56">
-        <v>3.20495482016</v>
+        <v>3.1601576872</v>
       </c>
       <c r="Q56">
-        <v>4.134954820159999</v>
+        <v>4.0901576872</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1877467650295079</v>
+        <v>0.1905010425372292</v>
       </c>
       <c r="T56">
-        <v>2.393426382187457</v>
+        <v>2.439867457822222</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.324884234023269</v>
+        <v>2.282613611586482</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1174098691417531</v>
+        <v>0.1173479063699326</v>
       </c>
       <c r="C57">
-        <v>38.55665322308584</v>
+        <v>37.84748070940786</v>
       </c>
       <c r="D57">
-        <v>79.03575322308583</v>
+        <v>79.10420070940786</v>
       </c>
       <c r="E57">
-        <v>42.6071</v>
+        <v>43.38472000000001</v>
       </c>
       <c r="F57">
-        <v>42.7691</v>
+        <v>43.54672000000001</v>
       </c>
       <c r="G57">
         <v>2.29</v>
@@ -6080,28 +6080,28 @@
         <v>7.4</v>
       </c>
       <c r="M57">
-        <v>3.24189778</v>
+        <v>3.300841376000001</v>
       </c>
       <c r="N57">
-        <v>4.15810222</v>
+        <v>4.099158623999999</v>
       </c>
       <c r="O57">
-        <v>0.9979445328</v>
+        <v>0.9837980697599998</v>
       </c>
       <c r="P57">
-        <v>3.1601576872</v>
+        <v>3.11536055424</v>
       </c>
       <c r="Q57">
-        <v>4.0901576872</v>
+        <v>4.045360554239999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1905010425372292</v>
+        <v>0.1933805144771196</v>
       </c>
       <c r="T57">
-        <v>2.439867457822222</v>
+        <v>2.488419491440385</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.282613611586482</v>
+        <v>2.241852654236723</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1173479063699326</v>
+        <v>0.1172859435981121</v>
       </c>
       <c r="C58">
-        <v>37.84748070940786</v>
+        <v>37.13842685390973</v>
       </c>
       <c r="D58">
-        <v>79.10420070940786</v>
+        <v>79.17276685390974</v>
       </c>
       <c r="E58">
-        <v>43.38472000000001</v>
+        <v>44.16234000000001</v>
       </c>
       <c r="F58">
-        <v>43.54672000000001</v>
+        <v>44.32434000000001</v>
       </c>
       <c r="G58">
         <v>2.29</v>
@@ -6162,28 +6162,28 @@
         <v>7.4</v>
       </c>
       <c r="M58">
-        <v>3.300841376000001</v>
+        <v>3.359784972000001</v>
       </c>
       <c r="N58">
-        <v>4.099158623999999</v>
+        <v>4.040215028</v>
       </c>
       <c r="O58">
-        <v>0.9837980697599998</v>
+        <v>0.9696516067199998</v>
       </c>
       <c r="P58">
-        <v>3.11536055424</v>
+        <v>3.07056342128</v>
       </c>
       <c r="Q58">
-        <v>4.045360554239999</v>
+        <v>4.000563421279999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1933805144771196</v>
+        <v>0.1963939153444468</v>
       </c>
       <c r="T58">
-        <v>2.488419491440385</v>
+        <v>2.539229759180323</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.241852654236723</v>
+        <v>2.202521905916781</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1172859435981121</v>
+        <v>0.1172239808262916</v>
       </c>
       <c r="C59">
-        <v>37.13842685390973</v>
+        <v>36.42949196541171</v>
       </c>
       <c r="D59">
-        <v>79.17276685390974</v>
+        <v>79.24145196541171</v>
       </c>
       <c r="E59">
-        <v>44.16234000000001</v>
+        <v>44.93996000000001</v>
       </c>
       <c r="F59">
-        <v>44.32434000000001</v>
+        <v>45.10196000000001</v>
       </c>
       <c r="G59">
         <v>2.29</v>
@@ -6244,28 +6244,28 @@
         <v>7.4</v>
       </c>
       <c r="M59">
-        <v>3.359784972000001</v>
+        <v>3.418728568000001</v>
       </c>
       <c r="N59">
-        <v>4.040215028</v>
+        <v>3.981271432</v>
       </c>
       <c r="O59">
-        <v>0.9696516067199998</v>
+        <v>0.9555051436799999</v>
       </c>
       <c r="P59">
-        <v>3.07056342128</v>
+        <v>3.02576628832</v>
       </c>
       <c r="Q59">
-        <v>4.000563421279999</v>
+        <v>3.95576628832</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1963939153444468</v>
+        <v>0.1995508114911704</v>
       </c>
       <c r="T59">
-        <v>2.539229759180323</v>
+        <v>2.592459563479306</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.202521905916781</v>
+        <v>2.164547390297527</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1172239808262916</v>
+        <v>0.1171620180544711</v>
       </c>
       <c r="C60">
-        <v>36.42949196541169</v>
+        <v>35.72067635380655</v>
       </c>
       <c r="D60">
-        <v>79.24145196541168</v>
+        <v>79.31025635380654</v>
       </c>
       <c r="E60">
-        <v>44.93996</v>
+        <v>45.71758</v>
       </c>
       <c r="F60">
-        <v>45.10196</v>
+        <v>45.87958</v>
       </c>
       <c r="G60">
         <v>2.29</v>
@@ -6326,28 +6326,28 @@
         <v>7.4</v>
       </c>
       <c r="M60">
-        <v>3.418728568</v>
+        <v>3.477672164</v>
       </c>
       <c r="N60">
-        <v>3.981271432</v>
+        <v>3.922327836</v>
       </c>
       <c r="O60">
-        <v>0.9555051436800001</v>
+        <v>0.9413586806400001</v>
       </c>
       <c r="P60">
-        <v>3.02576628832</v>
+        <v>2.98096915536</v>
       </c>
       <c r="Q60">
-        <v>3.95576628832</v>
+        <v>3.91096915536</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1995508114911704</v>
+        <v>0.2028617025718807</v>
       </c>
       <c r="T60">
-        <v>2.592459563479306</v>
+        <v>2.648285943597751</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.164547390297527</v>
+        <v>2.127860146394179</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1171620180544711</v>
+        <v>0.1171000552826506</v>
       </c>
       <c r="C61">
-        <v>35.72067635380655</v>
+        <v>35.0119803300643</v>
       </c>
       <c r="D61">
-        <v>79.31025635380654</v>
+        <v>79.37918033006429</v>
       </c>
       <c r="E61">
-        <v>45.71758</v>
+        <v>46.4952</v>
       </c>
       <c r="F61">
-        <v>45.87958</v>
+        <v>46.6572</v>
       </c>
       <c r="G61">
         <v>2.29</v>
@@ -6408,28 +6408,28 @@
         <v>7.4</v>
       </c>
       <c r="M61">
-        <v>3.477672164</v>
+        <v>3.53661576</v>
       </c>
       <c r="N61">
-        <v>3.922327836</v>
+        <v>3.86338424</v>
       </c>
       <c r="O61">
-        <v>0.9413586806400001</v>
+        <v>0.9272122176000001</v>
       </c>
       <c r="P61">
-        <v>2.98096915536</v>
+        <v>2.9361720224</v>
       </c>
       <c r="Q61">
-        <v>3.91096915536</v>
+        <v>3.8661720224</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2028617025718807</v>
+        <v>0.2063381382066264</v>
       </c>
       <c r="T61">
-        <v>2.648285943597751</v>
+        <v>2.706903642722119</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.127860146394179</v>
+        <v>2.092395810620943</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1171000552826506</v>
+        <v>0.1170380925108301</v>
       </c>
       <c r="C62">
-        <v>35.0119803300643</v>
+        <v>34.30340420623688</v>
       </c>
       <c r="D62">
-        <v>79.37918033006429</v>
+        <v>79.44822420623687</v>
       </c>
       <c r="E62">
-        <v>46.4952</v>
+        <v>47.27282</v>
       </c>
       <c r="F62">
-        <v>46.6572</v>
+        <v>47.43482</v>
       </c>
       <c r="G62">
         <v>2.29</v>
@@ -6490,28 +6490,28 @@
         <v>7.4</v>
       </c>
       <c r="M62">
-        <v>3.53661576</v>
+        <v>3.595559356</v>
       </c>
       <c r="N62">
-        <v>3.86338424</v>
+        <v>3.804440644</v>
       </c>
       <c r="O62">
-        <v>0.9272122176000001</v>
+        <v>0.9130657545599999</v>
       </c>
       <c r="P62">
-        <v>2.9361720224</v>
+        <v>2.89137488944</v>
       </c>
       <c r="Q62">
-        <v>3.8661720224</v>
+        <v>3.82137488944</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2063381382066264</v>
+        <v>0.2099928525918719</v>
       </c>
       <c r="T62">
-        <v>2.706903642722119</v>
+        <v>2.768527377699018</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.092395810620943</v>
+        <v>2.058094239955025</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1170380925108301</v>
+        <v>0.1169761297390095</v>
       </c>
       <c r="C63">
-        <v>34.30340420623688</v>
+        <v>33.59494829546297</v>
       </c>
       <c r="D63">
-        <v>79.44822420623687</v>
+        <v>79.51738829546296</v>
       </c>
       <c r="E63">
-        <v>47.27282</v>
+        <v>48.05044</v>
       </c>
       <c r="F63">
-        <v>47.43482</v>
+        <v>48.21244</v>
       </c>
       <c r="G63">
         <v>2.29</v>
@@ -6572,28 +6572,28 @@
         <v>7.4</v>
       </c>
       <c r="M63">
-        <v>3.595559356</v>
+        <v>3.654502952000001</v>
       </c>
       <c r="N63">
-        <v>3.804440644</v>
+        <v>3.745497048</v>
       </c>
       <c r="O63">
-        <v>0.9130657545599999</v>
+        <v>0.8989192915199999</v>
       </c>
       <c r="P63">
-        <v>2.89137488944</v>
+        <v>2.84657775648</v>
       </c>
       <c r="Q63">
-        <v>3.82137488944</v>
+        <v>3.77657775648</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2099928525918719</v>
+        <v>0.2138399203658145</v>
       </c>
       <c r="T63">
-        <v>2.768527377699018</v>
+        <v>2.833394467148386</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.058094239955025</v>
+        <v>2.024899171568654</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1169761297390095</v>
+        <v>0.123713126967189</v>
       </c>
       <c r="C64">
-        <v>33.59494829546297</v>
+        <v>25.94161369650709</v>
       </c>
       <c r="D64">
-        <v>79.51738829546296</v>
+        <v>72.64167369650708</v>
       </c>
       <c r="E64">
-        <v>48.05044</v>
+        <v>48.82806</v>
       </c>
       <c r="F64">
-        <v>48.21244</v>
+        <v>48.99006</v>
       </c>
       <c r="G64">
         <v>2.29</v>
@@ -6654,45 +6654,45 @@
         <v>7.4</v>
       </c>
       <c r="M64">
-        <v>3.654502952000001</v>
+        <v>4.4091054</v>
       </c>
       <c r="N64">
-        <v>3.745497048</v>
+        <v>2.990894600000001</v>
       </c>
       <c r="O64">
-        <v>0.8989192915199999</v>
+        <v>0.7178147040000001</v>
       </c>
       <c r="P64">
-        <v>2.84657775648</v>
+        <v>2.273079896</v>
       </c>
       <c r="Q64">
-        <v>3.77657775648</v>
+        <v>3.203079896</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2138399203658145</v>
+        <v>0.2178949377491595</v>
       </c>
       <c r="T64">
-        <v>2.833394467148386</v>
+        <v>2.901767885757179</v>
       </c>
       <c r="U64">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.024899171568654</v>
+        <v>1.678344999418703</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.123713126967189</v>
+        <v>0.1237590841953685</v>
       </c>
       <c r="C65">
-        <v>25.94161369650709</v>
+        <v>25.12117110555613</v>
       </c>
       <c r="D65">
-        <v>72.64167369650708</v>
+        <v>72.59885110555612</v>
       </c>
       <c r="E65">
-        <v>48.82806</v>
+        <v>49.60568</v>
       </c>
       <c r="F65">
-        <v>48.99006</v>
+        <v>49.76768</v>
       </c>
       <c r="G65">
         <v>2.29</v>
@@ -6736,28 +6736,28 @@
         <v>7.4</v>
       </c>
       <c r="M65">
-        <v>4.4091054</v>
+        <v>4.4790912</v>
       </c>
       <c r="N65">
-        <v>2.990894600000001</v>
+        <v>2.9209088</v>
       </c>
       <c r="O65">
-        <v>0.7178147040000001</v>
+        <v>0.7010181120000001</v>
       </c>
       <c r="P65">
-        <v>2.273079896</v>
+        <v>2.219890688</v>
       </c>
       <c r="Q65">
-        <v>3.203079896</v>
+        <v>3.149890688</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2178949377491595</v>
+        <v>0.2221752338760236</v>
       </c>
       <c r="T65">
-        <v>2.901767885757179</v>
+        <v>2.973939827622016</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.678344999418703</v>
+        <v>1.652120858802786</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1237590841953685</v>
+        <v>0.123805041423548</v>
       </c>
       <c r="C66">
-        <v>25.12117110555613</v>
+        <v>24.30077897307675</v>
       </c>
       <c r="D66">
-        <v>72.59885110555612</v>
+        <v>72.55607897307675</v>
       </c>
       <c r="E66">
-        <v>49.60568</v>
+        <v>50.38330000000001</v>
       </c>
       <c r="F66">
-        <v>49.76768</v>
+        <v>50.5453</v>
       </c>
       <c r="G66">
         <v>2.29</v>
@@ -6818,28 +6818,28 @@
         <v>7.4</v>
       </c>
       <c r="M66">
-        <v>4.4790912</v>
+        <v>4.549077</v>
       </c>
       <c r="N66">
-        <v>2.9209088</v>
+        <v>2.850923</v>
       </c>
       <c r="O66">
-        <v>0.7010181120000001</v>
+        <v>0.6842215199999999</v>
       </c>
       <c r="P66">
-        <v>2.219890688</v>
+        <v>2.16670148</v>
       </c>
       <c r="Q66">
-        <v>3.149890688</v>
+        <v>3.09670148</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2221752338760236</v>
+        <v>0.2267001183529943</v>
       </c>
       <c r="T66">
-        <v>2.973939827622016</v>
+        <v>3.050235880450559</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.652120858802786</v>
+        <v>1.626703614821204</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.123805041423548</v>
+        <v>0.1238509986517275</v>
       </c>
       <c r="C67">
-        <v>24.30077897307675</v>
+        <v>23.48043720993758</v>
       </c>
       <c r="D67">
-        <v>72.55607897307675</v>
+        <v>72.51335720993758</v>
       </c>
       <c r="E67">
-        <v>50.38330000000001</v>
+        <v>51.16092</v>
       </c>
       <c r="F67">
-        <v>50.5453</v>
+        <v>51.32292</v>
       </c>
       <c r="G67">
         <v>2.29</v>
@@ -6900,28 +6900,28 @@
         <v>7.4</v>
       </c>
       <c r="M67">
-        <v>4.549077</v>
+        <v>4.6190628</v>
       </c>
       <c r="N67">
-        <v>2.850923</v>
+        <v>2.7809372</v>
       </c>
       <c r="O67">
-        <v>0.6842215199999999</v>
+        <v>0.6674249280000001</v>
       </c>
       <c r="P67">
-        <v>2.16670148</v>
+        <v>2.113512272</v>
       </c>
       <c r="Q67">
-        <v>3.09670148</v>
+        <v>3.043512272</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2267001183529943</v>
+        <v>0.2314911725050808</v>
       </c>
       <c r="T67">
-        <v>3.050235880450559</v>
+        <v>3.131019936386663</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.626703614821204</v>
+        <v>1.602056590354217</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1238509986517275</v>
+        <v>0.123896955879907</v>
       </c>
       <c r="C68">
-        <v>23.48043720993758</v>
+        <v>22.66014572721702</v>
       </c>
       <c r="D68">
-        <v>72.51335720993758</v>
+        <v>72.47068572721702</v>
       </c>
       <c r="E68">
-        <v>51.16092</v>
+        <v>51.93854</v>
       </c>
       <c r="F68">
-        <v>51.32292</v>
+        <v>52.10054</v>
       </c>
       <c r="G68">
         <v>2.29</v>
@@ -6982,28 +6982,28 @@
         <v>7.4</v>
       </c>
       <c r="M68">
-        <v>4.6190628</v>
+        <v>4.6890486</v>
       </c>
       <c r="N68">
-        <v>2.7809372</v>
+        <v>2.7109514</v>
       </c>
       <c r="O68">
-        <v>0.6674249280000001</v>
+        <v>0.6506283359999999</v>
       </c>
       <c r="P68">
-        <v>2.113512272</v>
+        <v>2.060323064</v>
       </c>
       <c r="Q68">
-        <v>3.043512272</v>
+        <v>2.990323064</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2314911725050808</v>
+        <v>0.2365725935754756</v>
       </c>
       <c r="T68">
-        <v>3.131019936386663</v>
+        <v>3.216699995712833</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.602056590354217</v>
+        <v>1.57814529796087</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.123896955879907</v>
+        <v>0.1239429131080864</v>
       </c>
       <c r="C69">
-        <v>22.66014572721702</v>
+        <v>21.83990443620269</v>
       </c>
       <c r="D69">
-        <v>72.47068572721702</v>
+        <v>72.42806443620269</v>
       </c>
       <c r="E69">
-        <v>51.93854</v>
+        <v>52.71616</v>
       </c>
       <c r="F69">
-        <v>52.10054</v>
+        <v>52.87816</v>
       </c>
       <c r="G69">
         <v>2.29</v>
@@ -7064,28 +7064,28 @@
         <v>7.4</v>
       </c>
       <c r="M69">
-        <v>4.6890486</v>
+        <v>4.7590344</v>
       </c>
       <c r="N69">
-        <v>2.7109514</v>
+        <v>2.6409656</v>
       </c>
       <c r="O69">
-        <v>0.6506283359999999</v>
+        <v>0.6338317440000001</v>
       </c>
       <c r="P69">
-        <v>2.060323064</v>
+        <v>2.007133856</v>
       </c>
       <c r="Q69">
-        <v>2.990323064</v>
+        <v>2.937133856</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2365725935754756</v>
+        <v>0.2419716034627701</v>
       </c>
       <c r="T69">
-        <v>3.216699995712833</v>
+        <v>3.307735058746889</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.57814529796087</v>
+        <v>1.55493727887321</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1239429131080864</v>
+        <v>0.1239888703362659</v>
       </c>
       <c r="C70">
-        <v>21.83990443620269</v>
+        <v>21.01971324839066</v>
       </c>
       <c r="D70">
-        <v>72.42806443620269</v>
+        <v>72.38549324839066</v>
       </c>
       <c r="E70">
-        <v>52.71616</v>
+        <v>53.49378000000001</v>
       </c>
       <c r="F70">
-        <v>52.87816</v>
+        <v>53.65578000000001</v>
       </c>
       <c r="G70">
         <v>2.29</v>
@@ -7146,28 +7146,28 @@
         <v>7.4</v>
       </c>
       <c r="M70">
-        <v>4.7590344</v>
+        <v>4.8290202</v>
       </c>
       <c r="N70">
-        <v>2.6409656</v>
+        <v>2.5709798</v>
       </c>
       <c r="O70">
-        <v>0.6338317440000001</v>
+        <v>0.6170351519999999</v>
       </c>
       <c r="P70">
-        <v>2.007133856</v>
+        <v>1.953944648</v>
       </c>
       <c r="Q70">
-        <v>2.937133856</v>
+        <v>2.883944648</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2419716034627701</v>
+        <v>0.2477189365685998</v>
       </c>
       <c r="T70">
-        <v>3.307735058746889</v>
+        <v>3.40464335165411</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.55493727887321</v>
+        <v>1.53240195599099</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1239888703362659</v>
+        <v>0.1240348275644454</v>
       </c>
       <c r="C71">
-        <v>21.01971324839066</v>
+        <v>20.19957207548516</v>
       </c>
       <c r="D71">
-        <v>72.38549324839066</v>
+        <v>72.34297207548516</v>
       </c>
       <c r="E71">
-        <v>53.49378000000001</v>
+        <v>54.27140000000001</v>
       </c>
       <c r="F71">
-        <v>53.65578000000001</v>
+        <v>54.43340000000001</v>
       </c>
       <c r="G71">
         <v>2.29</v>
@@ -7228,28 +7228,28 @@
         <v>7.4</v>
       </c>
       <c r="M71">
-        <v>4.8290202</v>
+        <v>4.899006</v>
       </c>
       <c r="N71">
-        <v>2.5709798</v>
+        <v>2.500994</v>
       </c>
       <c r="O71">
-        <v>0.6170351519999999</v>
+        <v>0.6002385600000001</v>
       </c>
       <c r="P71">
-        <v>1.953944648</v>
+        <v>1.90075544</v>
       </c>
       <c r="Q71">
-        <v>2.883944648</v>
+        <v>2.83075544</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2477189365685998</v>
+        <v>0.253849425214818</v>
       </c>
       <c r="T71">
-        <v>3.40464335165411</v>
+        <v>3.508012197421812</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.53240195599099</v>
+        <v>1.510510499476833</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1240348275644454</v>
+        <v>0.1580177452628453</v>
       </c>
       <c r="C72">
-        <v>20.19957207548516</v>
+        <v>-2.485681697948245</v>
       </c>
       <c r="D72">
-        <v>72.34297207548516</v>
+        <v>50.43533830205176</v>
       </c>
       <c r="E72">
-        <v>54.27140000000001</v>
+        <v>55.04902000000001</v>
       </c>
       <c r="F72">
-        <v>54.43340000000001</v>
+        <v>55.21102</v>
       </c>
       <c r="G72">
         <v>2.29</v>
@@ -7310,45 +7310,45 @@
         <v>7.4</v>
       </c>
       <c r="M72">
-        <v>4.899006</v>
+        <v>8.104977736000002</v>
       </c>
       <c r="N72">
-        <v>2.500994</v>
+        <v>-0.7049777360000018</v>
       </c>
       <c r="O72">
-        <v>0.6002385600000001</v>
+        <v>-0.1691946566400004</v>
       </c>
       <c r="P72">
-        <v>1.90075544</v>
+        <v>-0.5357830793600014</v>
       </c>
       <c r="Q72">
-        <v>2.83075544</v>
+        <v>0.3942169206399984</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.253849425214818</v>
+        <v>0.2642367724652932</v>
       </c>
       <c r="T72">
-        <v>3.508012197421812</v>
+        <v>3.683157794752343</v>
       </c>
       <c r="U72">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.24</v>
+        <v>0.2191245994559015</v>
       </c>
       <c r="W72">
-        <v>0.0684</v>
+        <v>0.1146325087998737</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.510510499476833</v>
+        <v>0.9130191643995897</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1580177452628453</v>
+        <v>0.1590277452628453</v>
       </c>
       <c r="C73">
-        <v>-2.48568169794823</v>
+        <v>-3.713188707239297</v>
       </c>
       <c r="D73">
-        <v>50.43533830205177</v>
+        <v>49.9854512927607</v>
       </c>
       <c r="E73">
-        <v>55.04902</v>
+        <v>55.82664</v>
       </c>
       <c r="F73">
-        <v>55.21102</v>
+        <v>55.98864</v>
       </c>
       <c r="G73">
         <v>2.29</v>
@@ -7392,37 +7392,37 @@
         <v>7.4</v>
       </c>
       <c r="M73">
-        <v>8.104977736</v>
+        <v>8.219132352000001</v>
       </c>
       <c r="N73">
-        <v>-0.704977736</v>
+        <v>-0.8191323520000005</v>
       </c>
       <c r="O73">
-        <v>-0.16919465664</v>
+        <v>-0.1965917644800001</v>
       </c>
       <c r="P73">
-        <v>-0.53578307936</v>
+        <v>-0.6225405875200003</v>
       </c>
       <c r="Q73">
-        <v>0.3942169206399997</v>
+        <v>0.3074594124799994</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2642367724652931</v>
+        <v>0.2720380857676251</v>
       </c>
       <c r="T73">
-        <v>3.683157794752341</v>
+        <v>3.814699144564925</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2191245994559016</v>
+        <v>0.2160812022412363</v>
       </c>
       <c r="W73">
-        <v>0.1146325087998737</v>
+        <v>0.1150792795109865</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.91301916439959</v>
+        <v>0.9003383426718178</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1590277452628453</v>
+        <v>0.1600377452628453</v>
       </c>
       <c r="C74">
-        <v>-3.713188707239297</v>
+        <v>-4.932740624658784</v>
       </c>
       <c r="D74">
-        <v>49.9854512927607</v>
+        <v>49.54351937534121</v>
       </c>
       <c r="E74">
-        <v>55.82664</v>
+        <v>56.60426</v>
       </c>
       <c r="F74">
-        <v>55.98864</v>
+        <v>56.76626</v>
       </c>
       <c r="G74">
         <v>2.29</v>
@@ -7474,37 +7474,37 @@
         <v>7.4</v>
       </c>
       <c r="M74">
-        <v>8.219132352000001</v>
+        <v>8.333286967999999</v>
       </c>
       <c r="N74">
-        <v>-0.8191323520000005</v>
+        <v>-0.9332869679999991</v>
       </c>
       <c r="O74">
-        <v>-0.1965917644800001</v>
+        <v>-0.2239888723199998</v>
       </c>
       <c r="P74">
-        <v>-0.6225405875200003</v>
+        <v>-0.7092980956799994</v>
       </c>
       <c r="Q74">
-        <v>0.3074594124799994</v>
+        <v>0.2207019043200004</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2720380857676251</v>
+        <v>0.2804172741293889</v>
       </c>
       <c r="T74">
-        <v>3.814699144564925</v>
+        <v>3.95598429806733</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2160812022412363</v>
+        <v>0.2131211857721783</v>
       </c>
       <c r="W74">
-        <v>0.1150792795109865</v>
+        <v>0.1155138099286443</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9003383426718178</v>
+        <v>0.8880049407174094</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1600377452628453</v>
+        <v>0.1610477452628453</v>
       </c>
       <c r="C75">
-        <v>-4.932740624658784</v>
+        <v>-6.144546599013189</v>
       </c>
       <c r="D75">
-        <v>49.54351937534121</v>
+        <v>49.10933340098681</v>
       </c>
       <c r="E75">
-        <v>56.60426</v>
+        <v>57.38188</v>
       </c>
       <c r="F75">
-        <v>56.76626</v>
+        <v>57.54388</v>
       </c>
       <c r="G75">
         <v>2.29</v>
@@ -7556,37 +7556,37 @@
         <v>7.4</v>
       </c>
       <c r="M75">
-        <v>8.333286967999999</v>
+        <v>8.447441584000002</v>
       </c>
       <c r="N75">
-        <v>-0.9332869679999991</v>
+        <v>-1.047441584000001</v>
       </c>
       <c r="O75">
-        <v>-0.2239888723199998</v>
+        <v>-0.2513859801600003</v>
       </c>
       <c r="P75">
-        <v>-0.7092980956799994</v>
+        <v>-0.7960556038400011</v>
       </c>
       <c r="Q75">
-        <v>0.2207019043200004</v>
+        <v>0.1339443961599986</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2804172741293889</v>
+        <v>0.2894410154420577</v>
       </c>
       <c r="T75">
-        <v>3.95598429806733</v>
+        <v>4.108137540300689</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2131211857721783</v>
+        <v>0.2102411697482298</v>
       </c>
       <c r="W75">
-        <v>0.1155138099286443</v>
+        <v>0.1159365962809599</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8880049407174094</v>
+        <v>0.8760048739509577</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1610477452628453</v>
+        <v>0.1620577452628453</v>
       </c>
       <c r="C76">
-        <v>-6.144546599013189</v>
+        <v>-7.348808511109922</v>
       </c>
       <c r="D76">
-        <v>49.10933340098681</v>
+        <v>48.68269148889008</v>
       </c>
       <c r="E76">
-        <v>57.38188</v>
+        <v>58.1595</v>
       </c>
       <c r="F76">
-        <v>57.54388</v>
+        <v>58.3215</v>
       </c>
       <c r="G76">
         <v>2.29</v>
@@ -7638,37 +7638,37 @@
         <v>7.4</v>
       </c>
       <c r="M76">
-        <v>8.447441584000002</v>
+        <v>8.5615962</v>
       </c>
       <c r="N76">
-        <v>-1.047441584000001</v>
+        <v>-1.1615962</v>
       </c>
       <c r="O76">
-        <v>-0.2513859801600003</v>
+        <v>-0.278783088</v>
       </c>
       <c r="P76">
-        <v>-0.7960556038400011</v>
+        <v>-0.882813112</v>
       </c>
       <c r="Q76">
-        <v>0.1339443961599986</v>
+        <v>0.0471868879999997</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2894410154420577</v>
+        <v>0.29918665605974</v>
       </c>
       <c r="T76">
-        <v>4.108137540300689</v>
+        <v>4.272463041912716</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2102411697482298</v>
+        <v>0.2074379541515868</v>
       </c>
       <c r="W76">
-        <v>0.1159365962809599</v>
+        <v>0.1163481083305471</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8760048739509577</v>
+        <v>0.8643248089649451</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1620577452628453</v>
+        <v>0.1630677452628453</v>
       </c>
       <c r="C77">
-        <v>-7.348808511109922</v>
+        <v>-8.545721286745461</v>
       </c>
       <c r="D77">
-        <v>48.68269148889008</v>
+        <v>48.26339871325454</v>
       </c>
       <c r="E77">
-        <v>58.1595</v>
+        <v>58.93712</v>
       </c>
       <c r="F77">
-        <v>58.3215</v>
+        <v>59.09912</v>
       </c>
       <c r="G77">
         <v>2.29</v>
@@ -7720,37 +7720,37 @@
         <v>7.4</v>
       </c>
       <c r="M77">
-        <v>8.5615962</v>
+        <v>8.675750816000001</v>
       </c>
       <c r="N77">
-        <v>-1.1615962</v>
+        <v>-1.275750816</v>
       </c>
       <c r="O77">
-        <v>-0.278783088</v>
+        <v>-0.3061801958400001</v>
       </c>
       <c r="P77">
-        <v>-0.882813112</v>
+        <v>-0.9695706201600003</v>
       </c>
       <c r="Q77">
-        <v>0.0471868879999997</v>
+        <v>-0.03957062016000057</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.29918665605974</v>
+        <v>0.3097444333955626</v>
       </c>
       <c r="T77">
-        <v>4.272463041912716</v>
+        <v>4.450482335325747</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2074379541515868</v>
+        <v>0.2047085073864343</v>
       </c>
       <c r="W77">
-        <v>0.1163481083305471</v>
+        <v>0.1167487911156714</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8643248089649451</v>
+        <v>0.8529521141101432</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1630677452628453</v>
+        <v>0.1640777452628453</v>
       </c>
       <c r="C78">
-        <v>-8.545721286745461</v>
+        <v>-9.735473193657114</v>
       </c>
       <c r="D78">
-        <v>48.26339871325454</v>
+        <v>47.85126680634289</v>
       </c>
       <c r="E78">
-        <v>58.93712</v>
+        <v>59.71474000000001</v>
       </c>
       <c r="F78">
-        <v>59.09912</v>
+        <v>59.87674000000001</v>
       </c>
       <c r="G78">
         <v>2.29</v>
@@ -7802,37 +7802,37 @@
         <v>7.4</v>
       </c>
       <c r="M78">
-        <v>8.675750816000001</v>
+        <v>8.789905432000001</v>
       </c>
       <c r="N78">
-        <v>-1.275750816</v>
+        <v>-1.389905432000001</v>
       </c>
       <c r="O78">
-        <v>-0.3061801958400001</v>
+        <v>-0.3335773036800002</v>
       </c>
       <c r="P78">
-        <v>-0.9695706201600003</v>
+        <v>-1.056328128320001</v>
       </c>
       <c r="Q78">
-        <v>-0.03957062016000057</v>
+        <v>-0.1263281283200008</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3097444333955626</v>
+        <v>0.3212202783258044</v>
       </c>
       <c r="T78">
-        <v>4.450482335325747</v>
+        <v>4.643981567296431</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2047085073864343</v>
+        <v>0.2020499553424547</v>
       </c>
       <c r="W78">
-        <v>0.1167487911156714</v>
+        <v>0.1171390665557277</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8529521141101432</v>
+        <v>0.8418748139268946</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1640777452628453</v>
+        <v>0.1650877452628453</v>
       </c>
       <c r="C79">
-        <v>-9.735473193657114</v>
+        <v>-10.91824612338944</v>
       </c>
       <c r="D79">
-        <v>47.85126680634289</v>
+        <v>47.44611387661056</v>
       </c>
       <c r="E79">
-        <v>59.71474000000001</v>
+        <v>60.49236000000001</v>
       </c>
       <c r="F79">
-        <v>59.87674000000001</v>
+        <v>60.65436</v>
       </c>
       <c r="G79">
         <v>2.29</v>
@@ -7884,37 +7884,37 @@
         <v>7.4</v>
       </c>
       <c r="M79">
-        <v>8.789905432000001</v>
+        <v>8.904060048000002</v>
       </c>
       <c r="N79">
-        <v>-1.389905432000001</v>
+        <v>-1.504060048000001</v>
       </c>
       <c r="O79">
-        <v>-0.3335773036800002</v>
+        <v>-0.3609744115200003</v>
       </c>
       <c r="P79">
-        <v>-1.056328128320001</v>
+        <v>-1.143085636480001</v>
       </c>
       <c r="Q79">
-        <v>-0.1263281283200008</v>
+        <v>-0.2130856364800011</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3212202783258044</v>
+        <v>0.3337393818860683</v>
       </c>
       <c r="T79">
-        <v>4.643981567296431</v>
+        <v>4.855071638537178</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2020499553424547</v>
+        <v>0.1994595712996027</v>
       </c>
       <c r="W79">
-        <v>0.1171390665557277</v>
+        <v>0.1175193349332183</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8418748139268946</v>
+        <v>0.8310815470816779</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1650877452628453</v>
+        <v>0.1660977452628453</v>
       </c>
       <c r="C80">
-        <v>-10.91824612338944</v>
+        <v>-12.09421585896158</v>
       </c>
       <c r="D80">
-        <v>47.44611387661056</v>
+        <v>47.04776414103843</v>
       </c>
       <c r="E80">
-        <v>60.49236000000001</v>
+        <v>61.26998</v>
       </c>
       <c r="F80">
-        <v>60.65436</v>
+        <v>61.43198</v>
       </c>
       <c r="G80">
         <v>2.29</v>
@@ -7966,37 +7966,37 @@
         <v>7.4</v>
       </c>
       <c r="M80">
-        <v>8.904060048000002</v>
+        <v>9.018214664000002</v>
       </c>
       <c r="N80">
-        <v>-1.504060048000001</v>
+        <v>-1.618214664000002</v>
       </c>
       <c r="O80">
-        <v>-0.3609744115200003</v>
+        <v>-0.3883715193600004</v>
       </c>
       <c r="P80">
-        <v>-1.143085636480001</v>
+        <v>-1.229843144640001</v>
       </c>
       <c r="Q80">
-        <v>-0.2130856364800011</v>
+        <v>-0.2998431446400016</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3337393818860683</v>
+        <v>0.3474507810235001</v>
       </c>
       <c r="T80">
-        <v>4.855071638537178</v>
+        <v>5.086265526086568</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1994595712996027</v>
+        <v>0.1969347665996077</v>
       </c>
       <c r="W80">
-        <v>0.1175193349332183</v>
+        <v>0.1178899762631776</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8310815470816779</v>
+        <v>0.8205615274983655</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1660977452628453</v>
+        <v>0.1671077452628453</v>
       </c>
       <c r="C81">
-        <v>-12.09421585896158</v>
+        <v>-13.26355232916293</v>
       </c>
       <c r="D81">
-        <v>47.04776414103843</v>
+        <v>46.65604767083707</v>
       </c>
       <c r="E81">
-        <v>61.26998</v>
+        <v>62.0476</v>
       </c>
       <c r="F81">
-        <v>61.43198</v>
+        <v>62.2096</v>
       </c>
       <c r="G81">
         <v>2.29</v>
@@ -8048,37 +8048,37 @@
         <v>7.4</v>
       </c>
       <c r="M81">
-        <v>9.018214664000002</v>
+        <v>9.132369280000001</v>
       </c>
       <c r="N81">
-        <v>-1.618214664000002</v>
+        <v>-1.73236928</v>
       </c>
       <c r="O81">
-        <v>-0.3883715193600004</v>
+        <v>-0.4157686272000001</v>
       </c>
       <c r="P81">
-        <v>-1.229843144640001</v>
+        <v>-1.3166006528</v>
       </c>
       <c r="Q81">
-        <v>-0.2998431446400016</v>
+        <v>-0.3866006528000006</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3474507810235001</v>
+        <v>0.3625333200746751</v>
       </c>
       <c r="T81">
-        <v>5.086265526086568</v>
+        <v>5.340578802390896</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1969347665996077</v>
+        <v>0.1944730820171126</v>
       </c>
       <c r="W81">
-        <v>0.1178899762631776</v>
+        <v>0.1182513515598879</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8205615274983655</v>
+        <v>0.8103045084046361</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1671077452628453</v>
+        <v>0.1681177452628453</v>
       </c>
       <c r="C82">
-        <v>-13.26355232916293</v>
+        <v>-14.42641985025061</v>
       </c>
       <c r="D82">
-        <v>46.65604767083707</v>
+        <v>46.2708001497494</v>
       </c>
       <c r="E82">
-        <v>62.0476</v>
+        <v>62.82522000000001</v>
       </c>
       <c r="F82">
-        <v>62.2096</v>
+        <v>62.98722000000001</v>
       </c>
       <c r="G82">
         <v>2.29</v>
@@ -8130,37 +8130,37 @@
         <v>7.4</v>
       </c>
       <c r="M82">
-        <v>9.132369280000001</v>
+        <v>9.246523896000001</v>
       </c>
       <c r="N82">
-        <v>-1.73236928</v>
+        <v>-1.846523896000001</v>
       </c>
       <c r="O82">
-        <v>-0.4157686272000001</v>
+        <v>-0.4431657350400002</v>
       </c>
       <c r="P82">
-        <v>-1.3166006528</v>
+        <v>-1.403358160960001</v>
       </c>
       <c r="Q82">
-        <v>-0.3866006528000006</v>
+        <v>-0.4733581609600008</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3625333200746751</v>
+        <v>0.3792034948154475</v>
       </c>
       <c r="T82">
-        <v>5.340578802390896</v>
+        <v>5.621661897253575</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1944730820171126</v>
+        <v>0.1920721797699878</v>
       </c>
       <c r="W82">
-        <v>0.1182513515598879</v>
+        <v>0.1186038040097658</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8103045084046361</v>
+        <v>0.8003007490416157</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1681177452628453</v>
+        <v>0.2165464031769644</v>
       </c>
       <c r="C83">
-        <v>-14.42641985025061</v>
+        <v>-28.32778776043263</v>
       </c>
       <c r="D83">
-        <v>46.2708001497494</v>
+        <v>33.14705223956737</v>
       </c>
       <c r="E83">
-        <v>62.82522000000001</v>
+        <v>63.60284000000001</v>
       </c>
       <c r="F83">
-        <v>62.98722000000001</v>
+        <v>63.76484000000001</v>
       </c>
       <c r="G83">
         <v>2.29</v>
@@ -8212,45 +8212,45 @@
         <v>7.4</v>
       </c>
       <c r="M83">
-        <v>9.246523896000001</v>
+        <v>12.803979872</v>
       </c>
       <c r="N83">
-        <v>-1.846523896000001</v>
+        <v>-5.403979872000001</v>
       </c>
       <c r="O83">
-        <v>-0.4431657350400002</v>
+        <v>-1.29695516928</v>
       </c>
       <c r="P83">
-        <v>-1.403358160960001</v>
+        <v>-4.10702470272</v>
       </c>
       <c r="Q83">
-        <v>-0.4733581609600008</v>
+        <v>-3.177024702720001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3792034948154475</v>
+        <v>0.4151628996058561</v>
       </c>
       <c r="T83">
-        <v>5.621661897253575</v>
+        <v>6.22798912207783</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1920721797699878</v>
+        <v>0.1387068722189881</v>
       </c>
       <c r="W83">
-        <v>0.1186038040097658</v>
+        <v>0.1729476600584272</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8003007490416157</v>
+        <v>0.5779453009124504</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2165464031769644</v>
+        <v>0.2180964031769644</v>
       </c>
       <c r="C84">
-        <v>-28.32778776043263</v>
+        <v>-29.40360278960315</v>
       </c>
       <c r="D84">
-        <v>33.14705223956737</v>
+        <v>32.84885721039686</v>
       </c>
       <c r="E84">
-        <v>63.60284000000001</v>
+        <v>64.38046</v>
       </c>
       <c r="F84">
-        <v>63.76484000000001</v>
+        <v>64.54246000000001</v>
       </c>
       <c r="G84">
         <v>2.29</v>
@@ -8294,37 +8294,37 @@
         <v>7.4</v>
       </c>
       <c r="M84">
-        <v>12.803979872</v>
+        <v>12.960125968</v>
       </c>
       <c r="N84">
-        <v>-5.403979872000001</v>
+        <v>-5.560125968000001</v>
       </c>
       <c r="O84">
-        <v>-1.29695516928</v>
+        <v>-1.33443023232</v>
       </c>
       <c r="P84">
-        <v>-4.10702470272</v>
+        <v>-4.22569573568</v>
       </c>
       <c r="Q84">
-        <v>-3.177024702720001</v>
+        <v>-3.295695735680001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4151628996058561</v>
+        <v>0.4368901289944359</v>
       </c>
       <c r="T84">
-        <v>6.22798912207783</v>
+        <v>6.594341423376526</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1387068722189881</v>
+        <v>0.1370357050838196</v>
       </c>
       <c r="W84">
-        <v>0.1729476600584272</v>
+        <v>0.173283230419169</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5779453009124504</v>
+        <v>0.5709821045159149</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2180964031769644</v>
+        <v>0.2196464031769644</v>
       </c>
       <c r="C85">
-        <v>-29.40360278960315</v>
+        <v>-30.47410045486198</v>
       </c>
       <c r="D85">
-        <v>32.84885721039686</v>
+        <v>32.55597954513803</v>
       </c>
       <c r="E85">
-        <v>64.38046</v>
+        <v>65.15808</v>
       </c>
       <c r="F85">
-        <v>64.54246000000001</v>
+        <v>65.32008</v>
       </c>
       <c r="G85">
         <v>2.29</v>
@@ -8376,37 +8376,37 @@
         <v>7.4</v>
       </c>
       <c r="M85">
-        <v>12.960125968</v>
+        <v>13.116272064</v>
       </c>
       <c r="N85">
-        <v>-5.560125968000001</v>
+        <v>-5.716272064000002</v>
       </c>
       <c r="O85">
-        <v>-1.33443023232</v>
+        <v>-1.37190529536</v>
       </c>
       <c r="P85">
-        <v>-4.22569573568</v>
+        <v>-4.344366768640001</v>
       </c>
       <c r="Q85">
-        <v>-3.295695735680001</v>
+        <v>-3.414366768640002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4368901289944359</v>
+        <v>0.4613332620565883</v>
       </c>
       <c r="T85">
-        <v>6.594341423376526</v>
+        <v>7.00648776233756</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1370357050838196</v>
+        <v>0.1354043276423455</v>
       </c>
       <c r="W85">
-        <v>0.173283230419169</v>
+        <v>0.173610811009417</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5709821045159149</v>
+        <v>0.5641846985097732</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2196464031769644</v>
+        <v>0.2211964031769644</v>
       </c>
       <c r="C86">
-        <v>-30.47410045486198</v>
+        <v>-31.53942172684332</v>
       </c>
       <c r="D86">
-        <v>32.55597954513803</v>
+        <v>32.26827827315669</v>
       </c>
       <c r="E86">
-        <v>65.15808</v>
+        <v>65.9357</v>
       </c>
       <c r="F86">
-        <v>65.32008</v>
+        <v>66.0977</v>
       </c>
       <c r="G86">
         <v>2.29</v>
@@ -8458,37 +8458,37 @@
         <v>7.4</v>
       </c>
       <c r="M86">
-        <v>13.116272064</v>
+        <v>13.27241816</v>
       </c>
       <c r="N86">
-        <v>-5.716272064000002</v>
+        <v>-5.87241816</v>
       </c>
       <c r="O86">
-        <v>-1.37190529536</v>
+        <v>-1.4093803584</v>
       </c>
       <c r="P86">
-        <v>-4.344366768640001</v>
+        <v>-4.463037801600001</v>
       </c>
       <c r="Q86">
-        <v>-3.414366768640002</v>
+        <v>-3.533037801600001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.461333262056588</v>
+        <v>0.4890354795270271</v>
       </c>
       <c r="T86">
-        <v>7.006487762337556</v>
+        <v>7.473586946493392</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1354043276423455</v>
+        <v>0.1338113355524356</v>
       </c>
       <c r="W86">
-        <v>0.173610811009417</v>
+        <v>0.1739306838210709</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5641846985097732</v>
+        <v>0.5575472314684817</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2211964031769644</v>
+        <v>0.2227464031769643</v>
       </c>
       <c r="C87">
-        <v>-31.53942172684332</v>
+        <v>-32.59970263673122</v>
       </c>
       <c r="D87">
-        <v>32.26827827315669</v>
+        <v>31.98561736326878</v>
       </c>
       <c r="E87">
-        <v>65.9357</v>
+        <v>66.71332</v>
       </c>
       <c r="F87">
-        <v>66.0977</v>
+        <v>66.87532</v>
       </c>
       <c r="G87">
         <v>2.29</v>
@@ -8540,37 +8540,37 @@
         <v>7.4</v>
       </c>
       <c r="M87">
-        <v>13.27241816</v>
+        <v>13.428564256</v>
       </c>
       <c r="N87">
-        <v>-5.87241816</v>
+        <v>-6.028564256000001</v>
       </c>
       <c r="O87">
-        <v>-1.4093803584</v>
+        <v>-1.44685542144</v>
       </c>
       <c r="P87">
-        <v>-4.463037801600001</v>
+        <v>-4.581708834560001</v>
       </c>
       <c r="Q87">
-        <v>-3.533037801600001</v>
+        <v>-3.651708834560001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4890354795270271</v>
+        <v>0.5206951566361004</v>
       </c>
       <c r="T87">
-        <v>7.473586946493392</v>
+        <v>8.007414585528634</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1338113355524356</v>
+        <v>0.132255389790198</v>
       </c>
       <c r="W87">
-        <v>0.1739306838210709</v>
+        <v>0.1742431177301282</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5575472314684817</v>
+        <v>0.551064124125825</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2227464031769643</v>
+        <v>0.2242964031769644</v>
       </c>
       <c r="C88">
-        <v>-32.59970263673122</v>
+        <v>-33.65507449072188</v>
       </c>
       <c r="D88">
-        <v>31.98561736326878</v>
+        <v>31.70786550927812</v>
       </c>
       <c r="E88">
-        <v>66.71332</v>
+        <v>67.49093999999999</v>
       </c>
       <c r="F88">
-        <v>66.87532</v>
+        <v>67.65294</v>
       </c>
       <c r="G88">
         <v>2.29</v>
@@ -8622,37 +8622,37 @@
         <v>7.4</v>
       </c>
       <c r="M88">
-        <v>13.428564256</v>
+        <v>13.584710352</v>
       </c>
       <c r="N88">
-        <v>-6.028564256000001</v>
+        <v>-6.184710352</v>
       </c>
       <c r="O88">
-        <v>-1.44685542144</v>
+        <v>-1.48433048448</v>
       </c>
       <c r="P88">
-        <v>-4.581708834560001</v>
+        <v>-4.70037986752</v>
       </c>
       <c r="Q88">
-        <v>-3.651708834560001</v>
+        <v>-3.77037986752</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5206951566361004</v>
+        <v>0.5572255533004159</v>
       </c>
       <c r="T88">
-        <v>8.007414585528634</v>
+        <v>8.623369553646222</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.132255389790198</v>
+        <v>0.1307352128960578</v>
       </c>
       <c r="W88">
-        <v>0.1742431177301282</v>
+        <v>0.1745483692504716</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.551064124125825</v>
+        <v>0.5447300537335741</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2242964031769644</v>
+        <v>0.2258464031769644</v>
       </c>
       <c r="C89">
-        <v>-33.65507449072188</v>
+        <v>-34.70566407340816</v>
       </c>
       <c r="D89">
-        <v>31.70786550927812</v>
+        <v>31.43489592659184</v>
       </c>
       <c r="E89">
-        <v>67.49093999999999</v>
+        <v>68.26855999999999</v>
       </c>
       <c r="F89">
-        <v>67.65294</v>
+        <v>68.43056</v>
       </c>
       <c r="G89">
         <v>2.29</v>
@@ -8704,37 +8704,37 @@
         <v>7.4</v>
       </c>
       <c r="M89">
-        <v>13.584710352</v>
+        <v>13.740856448</v>
       </c>
       <c r="N89">
-        <v>-6.184710352</v>
+        <v>-6.340856448</v>
       </c>
       <c r="O89">
-        <v>-1.48433048448</v>
+        <v>-1.52180554752</v>
       </c>
       <c r="P89">
-        <v>-4.70037986752</v>
+        <v>-4.819050900480001</v>
       </c>
       <c r="Q89">
-        <v>-3.77037986752</v>
+        <v>-3.889050900480001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5572255533004159</v>
+        <v>0.5998443494087841</v>
       </c>
       <c r="T89">
-        <v>8.623369553646222</v>
+        <v>9.341983683116743</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1307352128960578</v>
+        <v>0.1292495854767844</v>
       </c>
       <c r="W89">
-        <v>0.1745483692504716</v>
+        <v>0.1748466832362617</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5447300537335741</v>
+        <v>0.5385399394866017</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2258464031769644</v>
+        <v>0.2273964031769644</v>
       </c>
       <c r="C90">
-        <v>-34.70566407340816</v>
+        <v>-35.75159384074829</v>
       </c>
       <c r="D90">
-        <v>31.43489592659184</v>
+        <v>31.16658615925171</v>
       </c>
       <c r="E90">
-        <v>68.26855999999999</v>
+        <v>69.04617999999999</v>
       </c>
       <c r="F90">
-        <v>68.43056</v>
+        <v>69.20818</v>
       </c>
       <c r="G90">
         <v>2.29</v>
@@ -8786,37 +8786,37 @@
         <v>7.4</v>
       </c>
       <c r="M90">
-        <v>13.740856448</v>
+        <v>13.897002544</v>
       </c>
       <c r="N90">
-        <v>-6.340856448</v>
+        <v>-6.497002543999999</v>
       </c>
       <c r="O90">
-        <v>-1.52180554752</v>
+        <v>-1.55928061056</v>
       </c>
       <c r="P90">
-        <v>-4.819050900480001</v>
+        <v>-4.937721933439999</v>
       </c>
       <c r="Q90">
-        <v>-3.889050900480001</v>
+        <v>-4.007721933439999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5998443494087841</v>
+        <v>0.6502120175368553</v>
       </c>
       <c r="T90">
-        <v>9.341983683116743</v>
+        <v>10.19125492703645</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1292495854767844</v>
+        <v>0.1277973429433374</v>
       </c>
       <c r="W90">
-        <v>0.1748466832362617</v>
+        <v>0.1751382935369779</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5385399394866017</v>
+        <v>0.5324889289305725</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2273964031769644</v>
+        <v>0.2289464031769644</v>
       </c>
       <c r="C91">
-        <v>-35.75159384074829</v>
+        <v>-36.79298210323589</v>
       </c>
       <c r="D91">
-        <v>31.16658615925171</v>
+        <v>30.90281789676411</v>
       </c>
       <c r="E91">
-        <v>69.04617999999999</v>
+        <v>69.82379999999999</v>
       </c>
       <c r="F91">
-        <v>69.20818</v>
+        <v>69.9858</v>
       </c>
       <c r="G91">
         <v>2.29</v>
@@ -8868,37 +8868,37 @@
         <v>7.4</v>
       </c>
       <c r="M91">
-        <v>13.897002544</v>
+        <v>14.05314864</v>
       </c>
       <c r="N91">
-        <v>-6.497002543999999</v>
+        <v>-6.65314864</v>
       </c>
       <c r="O91">
-        <v>-1.55928061056</v>
+        <v>-1.5967556736</v>
       </c>
       <c r="P91">
-        <v>-4.937721933439999</v>
+        <v>-5.0563929664</v>
       </c>
       <c r="Q91">
-        <v>-4.007721933439999</v>
+        <v>-4.1263929664</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6502120175368553</v>
+        <v>0.7106532192905409</v>
       </c>
       <c r="T91">
-        <v>10.19125492703645</v>
+        <v>11.21038041974009</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1277973429433374</v>
+        <v>0.1263773724661892</v>
       </c>
       <c r="W91">
-        <v>0.1751382935369779</v>
+        <v>0.1754234236087892</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5324889289305725</v>
+        <v>0.5265723852757883</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2289464031769644</v>
+        <v>0.2304964031769643</v>
       </c>
       <c r="C92">
-        <v>-36.79298210323589</v>
+        <v>-37.82994319984667</v>
       </c>
       <c r="D92">
-        <v>30.90281789676411</v>
+        <v>30.64347680015332</v>
       </c>
       <c r="E92">
-        <v>69.82379999999999</v>
+        <v>70.60141999999999</v>
       </c>
       <c r="F92">
-        <v>69.9858</v>
+        <v>70.76342</v>
       </c>
       <c r="G92">
         <v>2.29</v>
@@ -8950,37 +8950,37 @@
         <v>7.4</v>
       </c>
       <c r="M92">
-        <v>14.05314864</v>
+        <v>14.209294736</v>
       </c>
       <c r="N92">
-        <v>-6.65314864</v>
+        <v>-6.809294736</v>
       </c>
       <c r="O92">
-        <v>-1.5967556736</v>
+        <v>-1.63423073664</v>
       </c>
       <c r="P92">
-        <v>-5.0563929664</v>
+        <v>-5.17506399936</v>
       </c>
       <c r="Q92">
-        <v>-4.1263929664</v>
+        <v>-4.24506399936</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7106532192905409</v>
+        <v>0.7845257992117121</v>
       </c>
       <c r="T92">
-        <v>11.21038041974009</v>
+        <v>12.45597824415566</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1263773724661892</v>
+        <v>0.1249886101313959</v>
       </c>
       <c r="W92">
-        <v>0.1754234236087892</v>
+        <v>0.1757022870856157</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5265723852757883</v>
+        <v>0.5207858755474829</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2304964031769643</v>
+        <v>0.2320464031769644</v>
       </c>
       <c r="C93">
-        <v>-37.82994319984667</v>
+        <v>-38.8625876632996</v>
       </c>
       <c r="D93">
-        <v>30.64347680015332</v>
+        <v>30.38845233670041</v>
       </c>
       <c r="E93">
-        <v>70.60141999999999</v>
+        <v>71.37904</v>
       </c>
       <c r="F93">
-        <v>70.76342</v>
+        <v>71.54104000000001</v>
       </c>
       <c r="G93">
         <v>2.29</v>
@@ -9032,37 +9032,37 @@
         <v>7.4</v>
       </c>
       <c r="M93">
-        <v>14.209294736</v>
+        <v>14.365440832</v>
       </c>
       <c r="N93">
-        <v>-6.809294736</v>
+        <v>-6.965440832000002</v>
       </c>
       <c r="O93">
-        <v>-1.63423073664</v>
+        <v>-1.67170579968</v>
       </c>
       <c r="P93">
-        <v>-5.17506399936</v>
+        <v>-5.293735032320002</v>
       </c>
       <c r="Q93">
-        <v>-4.24506399936</v>
+        <v>-4.363735032320002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7845257992117121</v>
+        <v>0.8768665241131764</v>
       </c>
       <c r="T93">
-        <v>12.45597824415566</v>
+        <v>14.01297552467512</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1249886101313959</v>
+        <v>0.1236300382821416</v>
       </c>
       <c r="W93">
-        <v>0.1757022870856157</v>
+        <v>0.175975088312946</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5207858755474829</v>
+        <v>0.5151251595089232</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2320464031769644</v>
+        <v>0.2335964031769644</v>
       </c>
       <c r="C94">
-        <v>-38.8625876632996</v>
+        <v>-39.8910223771336</v>
       </c>
       <c r="D94">
-        <v>30.38845233670041</v>
+        <v>30.1376376228664</v>
       </c>
       <c r="E94">
-        <v>71.37904</v>
+        <v>72.15666</v>
       </c>
       <c r="F94">
-        <v>71.54104000000001</v>
+        <v>72.31866000000001</v>
       </c>
       <c r="G94">
         <v>2.29</v>
@@ -9114,37 +9114,37 @@
         <v>7.4</v>
       </c>
       <c r="M94">
-        <v>14.365440832</v>
+        <v>14.521586928</v>
       </c>
       <c r="N94">
-        <v>-6.965440832000002</v>
+        <v>-7.121586928000001</v>
       </c>
       <c r="O94">
-        <v>-1.67170579968</v>
+        <v>-1.70918086272</v>
       </c>
       <c r="P94">
-        <v>-5.293735032320002</v>
+        <v>-5.412406065280001</v>
       </c>
       <c r="Q94">
-        <v>-4.363735032320002</v>
+        <v>-4.482406065280001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8768665241131764</v>
+        <v>0.9955903132722018</v>
       </c>
       <c r="T94">
-        <v>14.01297552467512</v>
+        <v>16.01482917105728</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1236300382821416</v>
+        <v>0.122300683031796</v>
       </c>
       <c r="W94">
-        <v>0.175975088312946</v>
+        <v>0.1762420228472154</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5151251595089232</v>
+        <v>0.5095861792991498</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2335964031769644</v>
+        <v>0.2351464031769644</v>
       </c>
       <c r="C95">
-        <v>-39.8910223771336</v>
+        <v>-40.91535072506976</v>
       </c>
       <c r="D95">
-        <v>30.1376376228664</v>
+        <v>29.89092927493025</v>
       </c>
       <c r="E95">
-        <v>72.15666</v>
+        <v>72.93428</v>
       </c>
       <c r="F95">
-        <v>72.31866000000001</v>
+        <v>73.09628000000001</v>
       </c>
       <c r="G95">
         <v>2.29</v>
@@ -9196,37 +9196,37 @@
         <v>7.4</v>
       </c>
       <c r="M95">
-        <v>14.521586928</v>
+        <v>14.677733024</v>
       </c>
       <c r="N95">
-        <v>-7.121586928000001</v>
+        <v>-7.277733024000002</v>
       </c>
       <c r="O95">
-        <v>-1.70918086272</v>
+        <v>-1.74665592576</v>
       </c>
       <c r="P95">
-        <v>-5.412406065280001</v>
+        <v>-5.531077098240001</v>
       </c>
       <c r="Q95">
-        <v>-4.482406065280001</v>
+        <v>-4.601077098240001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9955903132722018</v>
+        <v>1.153888698817569</v>
       </c>
       <c r="T95">
-        <v>16.01482917105728</v>
+        <v>18.6839673662335</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.122300683031796</v>
+        <v>0.120999611935713</v>
       </c>
       <c r="W95">
-        <v>0.1762420228472154</v>
+        <v>0.1765032779233088</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5095861792991498</v>
+        <v>0.5041650497321377</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2351464031769644</v>
+        <v>0.2712128895560948</v>
       </c>
       <c r="C96">
-        <v>-40.91535072506976</v>
+        <v>-46.47557564032925</v>
       </c>
       <c r="D96">
-        <v>29.89092927493025</v>
+        <v>25.10832435967076</v>
       </c>
       <c r="E96">
-        <v>72.93428</v>
+        <v>73.7119</v>
       </c>
       <c r="F96">
-        <v>73.09628000000001</v>
+        <v>73.87390000000001</v>
       </c>
       <c r="G96">
         <v>2.29</v>
@@ -9278,45 +9278,45 @@
         <v>7.4</v>
       </c>
       <c r="M96">
-        <v>14.677733024</v>
+        <v>17.41946562</v>
       </c>
       <c r="N96">
-        <v>-7.277733024000002</v>
+        <v>-10.01946562</v>
       </c>
       <c r="O96">
-        <v>-1.74665592576</v>
+        <v>-2.4046717488</v>
       </c>
       <c r="P96">
-        <v>-5.531077098240001</v>
+        <v>-7.6147938712</v>
       </c>
       <c r="Q96">
-        <v>-4.601077098240001</v>
+        <v>-6.6847938712</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.153888698817569</v>
+        <v>1.400836166163693</v>
       </c>
       <c r="T96">
-        <v>18.6839673662335</v>
+        <v>22.84785643575699</v>
       </c>
       <c r="U96">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.120999611935713</v>
+        <v>0.101954907156331</v>
       </c>
       <c r="W96">
-        <v>0.1765032779233088</v>
+        <v>0.2117590328925371</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5041650497321377</v>
+        <v>0.4248121131513792</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2712128895560948</v>
+        <v>0.2731128895560949</v>
       </c>
       <c r="C97">
-        <v>-46.47557564032925</v>
+        <v>-47.46306414526329</v>
       </c>
       <c r="D97">
-        <v>25.10832435967076</v>
+        <v>24.89845585473671</v>
       </c>
       <c r="E97">
-        <v>73.7119</v>
+        <v>74.48952</v>
       </c>
       <c r="F97">
-        <v>73.87390000000001</v>
+        <v>74.65152</v>
       </c>
       <c r="G97">
         <v>2.29</v>
@@ -9360,37 +9360,37 @@
         <v>7.4</v>
       </c>
       <c r="M97">
-        <v>17.41946562</v>
+        <v>17.602828416</v>
       </c>
       <c r="N97">
-        <v>-10.01946562</v>
+        <v>-10.202828416</v>
       </c>
       <c r="O97">
-        <v>-2.4046717488</v>
+        <v>-2.44867881984</v>
       </c>
       <c r="P97">
-        <v>-7.6147938712</v>
+        <v>-7.754149596160001</v>
       </c>
       <c r="Q97">
-        <v>-6.6847938712</v>
+        <v>-6.824149596160002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.400836166163693</v>
+        <v>1.739595207704617</v>
       </c>
       <c r="T97">
-        <v>22.84785643575699</v>
+        <v>28.55982054469625</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.101954907156331</v>
+        <v>0.1008928768734526</v>
       </c>
       <c r="W97">
-        <v>0.2117590328925371</v>
+        <v>0.2120094596332399</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4248121131513792</v>
+        <v>0.420386986972719</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2731128895560948</v>
+        <v>0.2750128895560948</v>
       </c>
       <c r="C98">
-        <v>-47.46306414526327</v>
+        <v>-48.44707335058074</v>
       </c>
       <c r="D98">
-        <v>24.89845585473672</v>
+        <v>24.69206664941926</v>
       </c>
       <c r="E98">
-        <v>74.48951999999998</v>
+        <v>75.26714</v>
       </c>
       <c r="F98">
-        <v>74.65151999999999</v>
+        <v>75.42914</v>
       </c>
       <c r="G98">
         <v>2.29</v>
@@ -9442,37 +9442,37 @@
         <v>7.4</v>
       </c>
       <c r="M98">
-        <v>17.602828416</v>
+        <v>17.786191212</v>
       </c>
       <c r="N98">
-        <v>-10.202828416</v>
+        <v>-10.386191212</v>
       </c>
       <c r="O98">
-        <v>-2.448678819839999</v>
+        <v>-2.49268589088</v>
       </c>
       <c r="P98">
-        <v>-7.754149596159998</v>
+        <v>-7.893505321120001</v>
       </c>
       <c r="Q98">
-        <v>-6.824149596159998</v>
+        <v>-6.963505321120001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.739595207704612</v>
+        <v>2.304193610272816</v>
       </c>
       <c r="T98">
-        <v>28.55982054469617</v>
+        <v>38.07976072626158</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1008928768734526</v>
+        <v>0.09985274412217986</v>
       </c>
       <c r="W98">
-        <v>0.2120094596332399</v>
+        <v>0.21225472293599</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.420386986972719</v>
+        <v>0.4160531005090827</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2750128895560948</v>
+        <v>0.2769128895560948</v>
       </c>
       <c r="C99">
-        <v>-48.44707335058074</v>
+        <v>-49.42768906719355</v>
       </c>
       <c r="D99">
-        <v>24.69206664941926</v>
+        <v>24.48907093280645</v>
       </c>
       <c r="E99">
-        <v>75.26714</v>
+        <v>76.04476</v>
       </c>
       <c r="F99">
-        <v>75.42914</v>
+        <v>76.20676</v>
       </c>
       <c r="G99">
         <v>2.29</v>
@@ -9524,37 +9524,37 @@
         <v>7.4</v>
       </c>
       <c r="M99">
-        <v>17.786191212</v>
+        <v>17.969554008</v>
       </c>
       <c r="N99">
-        <v>-10.386191212</v>
+        <v>-10.569554008</v>
       </c>
       <c r="O99">
-        <v>-2.49268589088</v>
+        <v>-2.53669296192</v>
       </c>
       <c r="P99">
-        <v>-7.893505321120001</v>
+        <v>-8.032861046080003</v>
       </c>
       <c r="Q99">
-        <v>-6.963505321120001</v>
+        <v>-7.102861046080003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.304193610272816</v>
+        <v>3.433390415409223</v>
       </c>
       <c r="T99">
-        <v>38.07976072626158</v>
+        <v>57.11964108939235</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09985274412217986</v>
+        <v>0.09883383856991269</v>
       </c>
       <c r="W99">
-        <v>0.21225472293599</v>
+        <v>0.2124949808652146</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4160531005090827</v>
+        <v>0.4118076607079696</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2769128895560948</v>
+        <v>0.2788128895560948</v>
       </c>
       <c r="C100">
-        <v>-49.42768906719355</v>
+        <v>-50.40499430718594</v>
       </c>
       <c r="D100">
-        <v>24.48907093280645</v>
+        <v>24.28938569281405</v>
       </c>
       <c r="E100">
-        <v>76.04476</v>
+        <v>76.82238</v>
       </c>
       <c r="F100">
-        <v>76.20676</v>
+        <v>76.98438</v>
       </c>
       <c r="G100">
         <v>2.29</v>
@@ -9606,37 +9606,37 @@
         <v>7.4</v>
       </c>
       <c r="M100">
-        <v>17.969554008</v>
+        <v>18.152916804</v>
       </c>
       <c r="N100">
-        <v>-10.569554008</v>
+        <v>-10.752916804</v>
       </c>
       <c r="O100">
-        <v>-2.53669296192</v>
+        <v>-2.58070003296</v>
       </c>
       <c r="P100">
-        <v>-8.032861046080003</v>
+        <v>-8.17221677104</v>
       </c>
       <c r="Q100">
-        <v>-7.102861046080003</v>
+        <v>-7.242216771040001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.433390415409223</v>
+        <v>6.820980830818447</v>
       </c>
       <c r="T100">
-        <v>57.11964108939235</v>
+        <v>114.2392821787847</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09883383856991269</v>
+        <v>0.09783551696819644</v>
       </c>
       <c r="W100">
-        <v>0.2124949808652146</v>
+        <v>0.2127303850988993</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4118076607079696</v>
+        <v>0.4076479873674851</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2788128895560948</v>
-      </c>
-      <c r="C101">
-        <v>-50.40499430718594</v>
-      </c>
-      <c r="D101">
-        <v>24.28938569281405</v>
-      </c>
-      <c r="E101">
-        <v>76.82238</v>
-      </c>
-      <c r="F101">
-        <v>76.98438</v>
-      </c>
-      <c r="G101">
-        <v>2.29</v>
-      </c>
-      <c r="H101">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.33</v>
-      </c>
-      <c r="K101">
-        <v>0.9299999999999997</v>
-      </c>
-      <c r="L101">
-        <v>7.4</v>
-      </c>
-      <c r="M101">
-        <v>18.152916804</v>
-      </c>
-      <c r="N101">
-        <v>-10.752916804</v>
-      </c>
-      <c r="O101">
-        <v>-2.58070003296</v>
-      </c>
-      <c r="P101">
-        <v>-8.17221677104</v>
-      </c>
-      <c r="Q101">
-        <v>-7.242216771040001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.820980830818447</v>
-      </c>
-      <c r="T101">
-        <v>114.2392821787847</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09783551696819644</v>
-      </c>
-      <c r="W101">
-        <v>0.2127303850988993</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4076479873674851</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
